--- a/Бюджет.xlsx
+++ b/Бюджет.xlsx
@@ -1,58 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\Visual Studio 2022\Project\SE_script\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Мои документы\Visual Studio 2019\Project\Work\SE\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E3851A5-021B-4DB9-9EF7-0FE618C95C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="690" activeTab="3"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="690" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="22.12.2020" sheetId="35" r:id="rId1"/>
     <sheet name="Лист1" sheetId="32" r:id="rId2"/>
     <sheet name="Комуналка-1" sheetId="34" r:id="rId3"/>
     <sheet name="Комуналка-3" sheetId="2" r:id="rId4"/>
-    <sheet name="08.01.2020" sheetId="33" r:id="rId5"/>
-    <sheet name="07.04.2019" sheetId="31" r:id="rId6"/>
-    <sheet name="07.02.2019" sheetId="30" r:id="rId7"/>
-    <sheet name="22.01.2019" sheetId="29" r:id="rId8"/>
-    <sheet name="23.12.2018" sheetId="28" r:id="rId9"/>
-    <sheet name="22.10.2018" sheetId="27" r:id="rId10"/>
-    <sheet name="7.10.2018" sheetId="26" r:id="rId11"/>
-    <sheet name="23.09.2018" sheetId="25" r:id="rId12"/>
-    <sheet name="07.07.2018" sheetId="24" r:id="rId13"/>
-    <sheet name="22.06.2018" sheetId="23" r:id="rId14"/>
-    <sheet name="07.06.2018" sheetId="22" r:id="rId15"/>
-    <sheet name="22.05.2018" sheetId="21" r:id="rId16"/>
-    <sheet name="09.05.2018" sheetId="20" r:id="rId17"/>
-    <sheet name="22.04.2018" sheetId="19" r:id="rId18"/>
-    <sheet name="09.04.2018" sheetId="18" r:id="rId19"/>
-    <sheet name="22.03.2018" sheetId="17" r:id="rId20"/>
-    <sheet name="08.03.2018" sheetId="16" r:id="rId21"/>
-    <sheet name="22.02.2018" sheetId="15" r:id="rId22"/>
-    <sheet name="07.02.2018" sheetId="14" r:id="rId23"/>
-    <sheet name="28.01.2018" sheetId="13" r:id="rId24"/>
-    <sheet name="06.01.2018" sheetId="12" r:id="rId25"/>
-    <sheet name="22.12.2017" sheetId="11" r:id="rId26"/>
-    <sheet name="07.12.2017" sheetId="10" r:id="rId27"/>
-    <sheet name="22.11.2017" sheetId="9" r:id="rId28"/>
-    <sheet name="07.11.2017" sheetId="8" r:id="rId29"/>
-    <sheet name="21.10.2017" sheetId="7" r:id="rId30"/>
-    <sheet name="24.09.2017" sheetId="6" r:id="rId31"/>
-    <sheet name="22.06.2017" sheetId="5" r:id="rId32"/>
-    <sheet name="08.06.2017" sheetId="4" r:id="rId33"/>
-    <sheet name="24.04.2017" sheetId="1" r:id="rId34"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId35"/>
+    <sheet name="Лист2" sheetId="36" r:id="rId5"/>
+    <sheet name="08.01.2020" sheetId="33" r:id="rId6"/>
+    <sheet name="07.04.2019" sheetId="31" r:id="rId7"/>
+    <sheet name="07.02.2019" sheetId="30" r:id="rId8"/>
+    <sheet name="22.01.2019" sheetId="29" r:id="rId9"/>
+    <sheet name="23.12.2018" sheetId="28" r:id="rId10"/>
+    <sheet name="22.10.2018" sheetId="27" r:id="rId11"/>
+    <sheet name="7.10.2018" sheetId="26" r:id="rId12"/>
+    <sheet name="23.09.2018" sheetId="25" r:id="rId13"/>
+    <sheet name="07.07.2018" sheetId="24" r:id="rId14"/>
+    <sheet name="22.06.2018" sheetId="23" r:id="rId15"/>
+    <sheet name="07.06.2018" sheetId="22" r:id="rId16"/>
+    <sheet name="22.05.2018" sheetId="21" r:id="rId17"/>
+    <sheet name="09.05.2018" sheetId="20" r:id="rId18"/>
+    <sheet name="22.04.2018" sheetId="19" r:id="rId19"/>
+    <sheet name="09.04.2018" sheetId="18" r:id="rId20"/>
+    <sheet name="22.03.2018" sheetId="17" r:id="rId21"/>
+    <sheet name="08.03.2018" sheetId="16" r:id="rId22"/>
+    <sheet name="22.02.2018" sheetId="15" r:id="rId23"/>
+    <sheet name="07.02.2018" sheetId="14" r:id="rId24"/>
+    <sheet name="28.01.2018" sheetId="13" r:id="rId25"/>
+    <sheet name="06.01.2018" sheetId="12" r:id="rId26"/>
+    <sheet name="22.12.2017" sheetId="11" r:id="rId27"/>
+    <sheet name="07.12.2017" sheetId="10" r:id="rId28"/>
+    <sheet name="22.11.2017" sheetId="9" r:id="rId29"/>
+    <sheet name="07.11.2017" sheetId="8" r:id="rId30"/>
+    <sheet name="21.10.2017" sheetId="7" r:id="rId31"/>
+    <sheet name="24.09.2017" sheetId="6" r:id="rId32"/>
+    <sheet name="22.06.2017" sheetId="5" r:id="rId33"/>
+    <sheet name="08.06.2017" sheetId="4" r:id="rId34"/>
+    <sheet name="24.04.2017" sheetId="1" r:id="rId35"/>
+    <sheet name="Лист3" sheetId="3" r:id="rId36"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'22.12.2020'!$A$1:$M$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Комуналка-3'!$A$1:$ZD$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Комуналка-3'!$A$1:$ZN$26</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -61,6 +63,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -68,12 +72,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>RePack by Diakov</author>
   </authors>
   <commentList>
-    <comment ref="K7" authorId="0" shapeId="0">
+    <comment ref="K7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -104,12 +108,13 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>RePack by Diakov</author>
+    <author>tc={92005CF1-4D4D-4D02-979A-AEBF1D0B9C5F}</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -135,7 +140,15 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
+    <comment ref="YW4" authorId="1" shapeId="0" xr:uid="{92005CF1-4D4D-4D02-979A-AEBF1D0B9C5F}">
+      <text>
+        <t>[Цепочка примечаний]
+Ваша версия Excel позволяет прочитать эту цепочку примечаний, но если открыть файл в более поздней версии Excel, все внесенные в нее изменения будут удалены. Подробнее: https://go.microsoft.com/fwlink/?linkid=870924
+Комментарий:
+    При оплате указал 518</t>
+      </text>
+    </comment>
+    <comment ref="S10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -161,7 +174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA10" authorId="0" shapeId="0">
+    <comment ref="AA10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -187,7 +200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI10" authorId="0" shapeId="0">
+    <comment ref="AI10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -213,7 +226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AQ10" authorId="0" shapeId="0">
+    <comment ref="AQ10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -239,7 +252,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AY10" authorId="0" shapeId="0">
+    <comment ref="AY10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
@@ -265,7 +278,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BG10" authorId="0" shapeId="0">
+    <comment ref="BG10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -291,7 +304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BO10" authorId="0" shapeId="0">
+    <comment ref="BO10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
@@ -317,7 +330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BW10" authorId="0" shapeId="0">
+    <comment ref="BW10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -343,7 +356,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CE10" authorId="0" shapeId="0">
+    <comment ref="CE10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -369,7 +382,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CO10" authorId="0" shapeId="0">
+    <comment ref="CO10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -395,7 +408,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CW10" authorId="0" shapeId="0">
+    <comment ref="CW10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -421,7 +434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="DE10" authorId="0" shapeId="0">
+    <comment ref="DE10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -447,7 +460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="DM10" authorId="0" shapeId="0">
+    <comment ref="DM10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -473,7 +486,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="DU10" authorId="0" shapeId="0">
+    <comment ref="DU10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -499,7 +512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="EC10" authorId="0" shapeId="0">
+    <comment ref="EC10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000010000000}">
       <text>
         <r>
           <rPr>
@@ -525,7 +538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="EK10" authorId="0" shapeId="0">
+    <comment ref="EK10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000011000000}">
       <text>
         <r>
           <rPr>
@@ -551,7 +564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="ES10" authorId="0" shapeId="0">
+    <comment ref="ES10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000012000000}">
       <text>
         <r>
           <rPr>
@@ -577,7 +590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="FA10" authorId="0" shapeId="0">
+    <comment ref="FA10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000013000000}">
       <text>
         <r>
           <rPr>
@@ -603,7 +616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="FI10" authorId="0" shapeId="0">
+    <comment ref="FI10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000014000000}">
       <text>
         <r>
           <rPr>
@@ -629,7 +642,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="FQ10" authorId="0" shapeId="0">
+    <comment ref="FQ10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000015000000}">
       <text>
         <r>
           <rPr>
@@ -655,7 +668,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="FY10" authorId="0" shapeId="0">
+    <comment ref="FY10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000016000000}">
       <text>
         <r>
           <rPr>
@@ -681,7 +694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="GG10" authorId="0" shapeId="0">
+    <comment ref="GG10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000017000000}">
       <text>
         <r>
           <rPr>
@@ -707,7 +720,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="GO10" authorId="0" shapeId="0">
+    <comment ref="GO10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000018000000}">
       <text>
         <r>
           <rPr>
@@ -733,7 +746,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="GW10" authorId="0" shapeId="0">
+    <comment ref="GW10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000019000000}">
       <text>
         <r>
           <rPr>
@@ -759,7 +772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="HE10" authorId="0" shapeId="0">
+    <comment ref="HE10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001A000000}">
       <text>
         <r>
           <rPr>
@@ -785,7 +798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="HM10" authorId="0" shapeId="0">
+    <comment ref="HM10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -811,7 +824,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="HU10" authorId="0" shapeId="0">
+    <comment ref="HU10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001C000000}">
       <text>
         <r>
           <rPr>
@@ -837,7 +850,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="IC10" authorId="0" shapeId="0">
+    <comment ref="IC10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001D000000}">
       <text>
         <r>
           <rPr>
@@ -863,7 +876,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="IK10" authorId="0" shapeId="0">
+    <comment ref="IK10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -889,7 +902,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="IS10" authorId="0" shapeId="0">
+    <comment ref="IS10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -915,7 +928,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="JA10" authorId="0" shapeId="0">
+    <comment ref="JA10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000020000000}">
       <text>
         <r>
           <rPr>
@@ -941,7 +954,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="JI10" authorId="0" shapeId="0">
+    <comment ref="JI10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000021000000}">
       <text>
         <r>
           <rPr>
@@ -967,7 +980,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="JQ10" authorId="0" shapeId="0">
+    <comment ref="JQ10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000022000000}">
       <text>
         <r>
           <rPr>
@@ -993,7 +1006,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="JY10" authorId="0" shapeId="0">
+    <comment ref="JY10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000023000000}">
       <text>
         <r>
           <rPr>
@@ -1019,7 +1032,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="KG10" authorId="0" shapeId="0">
+    <comment ref="KG10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000024000000}">
       <text>
         <r>
           <rPr>
@@ -1045,7 +1058,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="KO10" authorId="0" shapeId="0">
+    <comment ref="KO10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000025000000}">
       <text>
         <r>
           <rPr>
@@ -1071,7 +1084,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="KW10" authorId="0" shapeId="0">
+    <comment ref="KW10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000026000000}">
       <text>
         <r>
           <rPr>
@@ -1097,7 +1110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="LE10" authorId="0" shapeId="0">
+    <comment ref="LE10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000027000000}">
       <text>
         <r>
           <rPr>
@@ -1123,7 +1136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="LM10" authorId="0" shapeId="0">
+    <comment ref="LM10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000028000000}">
       <text>
         <r>
           <rPr>
@@ -1149,7 +1162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="LU10" authorId="0" shapeId="0">
+    <comment ref="LU10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000029000000}">
       <text>
         <r>
           <rPr>
@@ -1175,7 +1188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="MC10" authorId="0" shapeId="0">
+    <comment ref="MC10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00002A000000}">
       <text>
         <r>
           <rPr>
@@ -1201,7 +1214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="ML10" authorId="0" shapeId="0">
+    <comment ref="ML10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00002B000000}">
       <text>
         <r>
           <rPr>
@@ -1227,7 +1240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="MT10" authorId="0" shapeId="0">
+    <comment ref="MT10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00002C000000}">
       <text>
         <r>
           <rPr>
@@ -1253,7 +1266,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="NB10" authorId="0" shapeId="0">
+    <comment ref="NB10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00002D000000}">
       <text>
         <r>
           <rPr>
@@ -1279,7 +1292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="NJ10" authorId="0" shapeId="0">
+    <comment ref="NJ10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00002E000000}">
       <text>
         <r>
           <rPr>
@@ -1305,7 +1318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="NR10" authorId="0" shapeId="0">
+    <comment ref="NR10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00002F000000}">
       <text>
         <r>
           <rPr>
@@ -1331,7 +1344,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="NZ10" authorId="0" shapeId="0">
+    <comment ref="NZ10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000030000000}">
       <text>
         <r>
           <rPr>
@@ -1357,7 +1370,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="OH10" authorId="0" shapeId="0">
+    <comment ref="OH10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000031000000}">
       <text>
         <r>
           <rPr>
@@ -1383,7 +1396,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="OP10" authorId="0" shapeId="0">
+    <comment ref="OP10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000032000000}">
       <text>
         <r>
           <rPr>
@@ -1409,7 +1422,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="OX10" authorId="0" shapeId="0">
+    <comment ref="OX10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000033000000}">
       <text>
         <r>
           <rPr>
@@ -1435,7 +1448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="PF10" authorId="0" shapeId="0">
+    <comment ref="PF10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000034000000}">
       <text>
         <r>
           <rPr>
@@ -1461,7 +1474,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="PN10" authorId="0" shapeId="0">
+    <comment ref="PN10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000035000000}">
       <text>
         <r>
           <rPr>
@@ -1487,7 +1500,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="PV10" authorId="0" shapeId="0">
+    <comment ref="PV10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000036000000}">
       <text>
         <r>
           <rPr>
@@ -1513,7 +1526,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="QE10" authorId="0" shapeId="0">
+    <comment ref="QE10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000037000000}">
       <text>
         <r>
           <rPr>
@@ -1539,7 +1552,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="QM10" authorId="0" shapeId="0">
+    <comment ref="QM10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000038000000}">
       <text>
         <r>
           <rPr>
@@ -1565,7 +1578,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="QV10" authorId="0" shapeId="0">
+    <comment ref="QV10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000039000000}">
       <text>
         <r>
           <rPr>
@@ -1591,7 +1604,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="RD10" authorId="0" shapeId="0">
+    <comment ref="RD10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00003A000000}">
       <text>
         <r>
           <rPr>
@@ -1617,7 +1630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="RM10" authorId="0" shapeId="0">
+    <comment ref="RM10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00003B000000}">
       <text>
         <r>
           <rPr>
@@ -1643,7 +1656,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="RV10" authorId="0" shapeId="0">
+    <comment ref="RV10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00003C000000}">
       <text>
         <r>
           <rPr>
@@ -1669,7 +1682,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="SE10" authorId="0" shapeId="0">
+    <comment ref="SE10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00003D000000}">
       <text>
         <r>
           <rPr>
@@ -1695,7 +1708,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="SN10" authorId="0" shapeId="0">
+    <comment ref="SN10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00003E000000}">
       <text>
         <r>
           <rPr>
@@ -1721,7 +1734,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="SW10" authorId="0" shapeId="0">
+    <comment ref="SW10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00003F000000}">
       <text>
         <r>
           <rPr>
@@ -1747,7 +1760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="TF10" authorId="0" shapeId="0">
+    <comment ref="TF10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000040000000}">
       <text>
         <r>
           <rPr>
@@ -1773,7 +1786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="TO10" authorId="0" shapeId="0">
+    <comment ref="TO10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000041000000}">
       <text>
         <r>
           <rPr>
@@ -1799,7 +1812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="TX10" authorId="0" shapeId="0">
+    <comment ref="TX10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000042000000}">
       <text>
         <r>
           <rPr>
@@ -1825,7 +1838,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="UG10" authorId="0" shapeId="0">
+    <comment ref="UG10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000043000000}">
       <text>
         <r>
           <rPr>
@@ -1851,7 +1864,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="UP10" authorId="0" shapeId="0">
+    <comment ref="UP10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000044000000}">
       <text>
         <r>
           <rPr>
@@ -1877,7 +1890,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="UY10" authorId="0" shapeId="0">
+    <comment ref="UY10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000045000000}">
       <text>
         <r>
           <rPr>
@@ -1903,7 +1916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="VH10" authorId="0" shapeId="0">
+    <comment ref="VH10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000046000000}">
       <text>
         <r>
           <rPr>
@@ -1929,7 +1942,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="VQ10" authorId="0" shapeId="0">
+    <comment ref="VQ10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000047000000}">
       <text>
         <r>
           <rPr>
@@ -1955,7 +1968,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="VZ10" authorId="0" shapeId="0">
+    <comment ref="VZ10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000048000000}">
       <text>
         <r>
           <rPr>
@@ -1981,7 +1994,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="WI10" authorId="0" shapeId="0">
+    <comment ref="WI10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000049000000}">
       <text>
         <r>
           <rPr>
@@ -2007,7 +2020,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="WR10" authorId="0" shapeId="0">
+    <comment ref="WR10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00004A000000}">
       <text>
         <r>
           <rPr>
@@ -2033,7 +2046,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="XA10" authorId="0" shapeId="0">
+    <comment ref="XA10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00004B000000}">
       <text>
         <r>
           <rPr>
@@ -2059,7 +2072,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="XJ10" authorId="0" shapeId="0">
+    <comment ref="XJ10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00004C000000}">
       <text>
         <r>
           <rPr>
@@ -2085,7 +2098,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="XS10" authorId="0" shapeId="0">
+    <comment ref="XS10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00004D000000}">
       <text>
         <r>
           <rPr>
@@ -2111,7 +2124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="YB10" authorId="0" shapeId="0">
+    <comment ref="YB10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00004E000000}">
       <text>
         <r>
           <rPr>
@@ -2137,7 +2150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="YK10" authorId="0" shapeId="0">
+    <comment ref="YK10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00004F000000}">
       <text>
         <r>
           <rPr>
@@ -2163,7 +2176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="YT10" authorId="0" shapeId="0">
+    <comment ref="YT10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000050000000}">
       <text>
         <r>
           <rPr>
@@ -2189,7 +2202,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="ZC10" authorId="0" shapeId="0">
+    <comment ref="ZC10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000051000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>RePack by Diakov:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Сумма на сайте (16150)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="ZL10" authorId="0" shapeId="0" xr:uid="{0975FDFA-F361-421D-833C-E17D9A74446E}">
       <text>
         <r>
           <rPr>
@@ -2220,7 +2259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="238">
   <si>
     <t>Статья расхода</t>
   </si>
@@ -2932,18 +2971,21 @@
   <si>
     <t>АТ "Крив. теплоцентраль" (плата за абон.обслуговування)</t>
   </si>
+  <si>
+    <t>непл</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₴_-;\-* #,##0.00\ _₴_-;_-* &quot;-&quot;??\ _₴_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_₴_-;\-* #,##0.00_₴_-;_-* &quot;-&quot;??_₴_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00\ _₽"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₴_-;\-* #,##0.00\ _₴_-;_-* &quot;-&quot;??\ _₴_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_₴_-;\-* #,##0.00_₴_-;_-* &quot;-&quot;??_₴_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00\ _₽"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3135,6 +3177,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -3875,7 +3923,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="339">
+  <cellXfs count="340">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3889,7 +3937,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -3897,13 +3945,13 @@
     <xf numFmtId="1" fontId="1" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3916,58 +3964,58 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3979,11 +4027,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3996,47 +4044,47 @@
     <xf numFmtId="49" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="8" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="1" fillId="8" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="8" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="8" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="8" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="8" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="8" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="8" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="7" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="7" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="17" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="17" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4063,10 +4111,10 @@
     <xf numFmtId="1" fontId="7" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4077,7 +4125,7 @@
     <xf numFmtId="1" fontId="8" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4093,48 +4141,48 @@
     <xf numFmtId="1" fontId="7" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="0" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3"/>
     <xf numFmtId="4" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4142,52 +4190,52 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="3" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="33" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="33" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="21" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="21" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="34" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="34" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4208,43 +4256,43 @@
     <xf numFmtId="1" fontId="7" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="10" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="10" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="40" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="40" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="29" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="29" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
@@ -4263,17 +4311,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="43" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="43" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="43" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="44" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="44" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4282,16 +4330,16 @@
     <xf numFmtId="1" fontId="7" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="7" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4300,13 +4348,13 @@
     <xf numFmtId="1" fontId="7" fillId="7" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -4315,66 +4363,66 @@
     <xf numFmtId="1" fontId="2" fillId="2" borderId="46" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="9" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="9" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="17" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="3" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="20" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="20" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="48" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="48" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="4" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4382,31 +4430,31 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="18" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="4" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="18" fillId="4" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="39" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="39" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="2" applyBorder="1"/>
@@ -4419,7 +4467,7 @@
     <xf numFmtId="1" fontId="7" fillId="7" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="21" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4432,111 +4480,111 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="9" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="9" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="50" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="50" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="19" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="19" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="18" fillId="4" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="4" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="41" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="41" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="18" fillId="4" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="18" fillId="4" borderId="52" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="52" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="1" applyFont="1" applyBorder="1"/>
@@ -4552,13 +4600,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="7" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4567,55 +4615,55 @@
     <xf numFmtId="1" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="10" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="10" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="10" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="10" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="10" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="10" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="13" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="17" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="17" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="29" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="29" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="29" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="29" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4633,20 +4681,20 @@
     <xf numFmtId="1" fontId="13" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4689,6 +4737,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="28" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Вывод" xfId="4" builtinId="21"/>
@@ -4710,10 +4759,16 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Levchenko, Eduard A" id="{CDB7AE87-53F8-4024-94D8-8DB81DA86166}" userId="S::eduard.levchenko@arcelormittal.com::4f20db7b-d9f9-4a6a-b507-a433dccf9de0" providerId="AD"/>
+</personList>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4751,9 +4806,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4788,7 +4843,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4823,7 +4878,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4995,8 +5050,16 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="YW4" dT="2024-06-10T10:14:31.56" personId="{CDB7AE87-53F8-4024-94D8-8DB81DA86166}" id="{92005CF1-4D4D-4D02-979A-AEBF1D0B9C5F}">
+    <text>При оплате указал 518</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5557,7 +5620,408 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A2:M19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2">
+        <v>43077</v>
+      </c>
+      <c r="D2" s="2">
+        <v>43091</v>
+      </c>
+      <c r="E2" s="3">
+        <f>D2-C2</f>
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="325" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="326"/>
+      <c r="D3" s="326"/>
+      <c r="E3" s="334"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5">
+        <v>6900</v>
+      </c>
+      <c r="D4" s="6">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6">
+        <f>C4*D4</f>
+        <v>6900</v>
+      </c>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="105"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6">
+        <f>C5*D5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="327" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="328"/>
+      <c r="D6" s="328"/>
+      <c r="E6" s="335"/>
+    </row>
+    <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="124" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="125" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="126">
+        <v>0</v>
+      </c>
+      <c r="D7" s="127">
+        <v>0</v>
+      </c>
+      <c r="E7" s="147">
+        <f>C7*D7</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="151"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="150"/>
+      <c r="K7" s="150"/>
+      <c r="L7" s="150"/>
+      <c r="M7" s="150"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="103" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="9">
+        <v>500</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="148">
+        <f t="shared" ref="E8:E16" si="0">C8*D8</f>
+        <v>500</v>
+      </c>
+      <c r="F8" s="150"/>
+      <c r="G8" s="150"/>
+      <c r="H8" s="150"/>
+      <c r="I8" s="150"/>
+      <c r="J8" s="150"/>
+      <c r="K8" s="150"/>
+      <c r="L8" s="150"/>
+      <c r="M8" s="150"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="103"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="148"/>
+      <c r="F9" s="150"/>
+      <c r="G9" s="150"/>
+      <c r="H9" s="150"/>
+      <c r="I9" s="150"/>
+      <c r="J9" s="150"/>
+      <c r="K9" s="150"/>
+      <c r="L9" s="150"/>
+      <c r="M9" s="150"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="103" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0</v>
+      </c>
+      <c r="E10" s="148">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="150"/>
+      <c r="G10" s="150"/>
+      <c r="H10" s="151"/>
+      <c r="I10" s="150"/>
+      <c r="J10" s="150"/>
+      <c r="K10" s="150"/>
+      <c r="L10" s="150"/>
+      <c r="M10" s="150"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="103"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="148">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="150"/>
+      <c r="G11" s="150"/>
+      <c r="H11" s="150"/>
+      <c r="I11" s="150"/>
+      <c r="J11" s="150"/>
+      <c r="K11" s="150"/>
+      <c r="L11" s="150"/>
+      <c r="M11" s="150"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="103" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0</v>
+      </c>
+      <c r="E12" s="148">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="150"/>
+      <c r="G12" s="150"/>
+      <c r="H12" s="150"/>
+      <c r="I12" s="151"/>
+      <c r="J12" s="150"/>
+      <c r="K12" s="150"/>
+      <c r="L12" s="150"/>
+      <c r="M12" s="150"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="103"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="9">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="148">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="150"/>
+      <c r="G13" s="150"/>
+      <c r="H13" s="150"/>
+      <c r="I13" s="151"/>
+      <c r="J13" s="150"/>
+      <c r="K13" s="150"/>
+      <c r="L13" s="150"/>
+      <c r="M13" s="150"/>
+    </row>
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="103" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="9">
+        <v>2400</v>
+      </c>
+      <c r="D14" s="8">
+        <v>1</v>
+      </c>
+      <c r="E14" s="148">
+        <f t="shared" si="0"/>
+        <v>2400</v>
+      </c>
+      <c r="F14" s="150"/>
+      <c r="G14" s="150"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="150"/>
+      <c r="J14" s="150"/>
+      <c r="K14" s="151"/>
+      <c r="L14" s="150"/>
+      <c r="M14" s="150"/>
+    </row>
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="103"/>
+      <c r="B15" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" s="9">
+        <v>1000</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1</v>
+      </c>
+      <c r="E15" s="148">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="F15" s="150"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="150"/>
+      <c r="I15" s="150"/>
+      <c r="J15" s="150"/>
+      <c r="K15" s="149"/>
+      <c r="L15" s="150"/>
+      <c r="M15" s="150"/>
+    </row>
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="103"/>
+      <c r="B16" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C16" s="9">
+        <v>500</v>
+      </c>
+      <c r="D16" s="8">
+        <v>1</v>
+      </c>
+      <c r="E16" s="148">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="F16" s="150"/>
+      <c r="G16" s="150"/>
+      <c r="H16" s="150"/>
+      <c r="I16" s="150"/>
+      <c r="J16" s="150"/>
+      <c r="K16" s="149"/>
+      <c r="L16" s="150"/>
+      <c r="M16" s="150"/>
+    </row>
+    <row r="17" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="92">
+        <f>SUM(E4:E5)</f>
+        <v>6900</v>
+      </c>
+      <c r="F17" s="88">
+        <f t="shared" ref="F17:K17" si="1">SUM(F3:F16)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="88">
+        <f>SUM(L7:L16)</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="93">
+        <f>SUM(F17:L17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E18" s="41">
+        <f>SUM(E7:E16)</f>
+        <v>4400</v>
+      </c>
+      <c r="J18" s="88"/>
+    </row>
+    <row r="19" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E19" s="43">
+        <f>E17-E18</f>
+        <v>2500</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B6:E6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A2:M23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6020,8 +6484,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A2:M22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6388,8 +6852,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A2:T26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6834,8 +7298,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A2:M21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7187,8 +7651,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A2:M20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7559,8 +8023,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A2:X37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8128,8 +8592,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A2:Y41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8748,8 +9212,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A2:Y46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9459,8 +9923,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A2:V46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10111,8 +10575,531 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A2:G27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>800000690090</v>
+      </c>
+      <c r="B2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2">
+        <v>246.58</v>
+      </c>
+      <c r="E2">
+        <v>669.45</v>
+      </c>
+      <c r="F2">
+        <v>381.07</v>
+      </c>
+      <c r="G2">
+        <f>E2-F2</f>
+        <v>288.38000000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1010006090</v>
+      </c>
+      <c r="B3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G3" t="e">
+        <f t="shared" ref="G3:G13" si="0">E3-F3</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1010006090</v>
+      </c>
+      <c r="B4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F4">
+        <v>500</v>
+      </c>
+      <c r="G4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>18300690090</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5">
+        <v>222.46</v>
+      </c>
+      <c r="E5">
+        <v>495.55</v>
+      </c>
+      <c r="F5">
+        <v>246.09</v>
+      </c>
+      <c r="G5" s="88">
+        <f t="shared" si="0"/>
+        <v>249.46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>18300690090</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6">
+        <v>222.46</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>8071090</v>
+      </c>
+      <c r="B7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7">
+        <v>498.24</v>
+      </c>
+      <c r="E7">
+        <v>498.24</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>498.24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>330152984</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>88.05</v>
+      </c>
+      <c r="E8">
+        <v>220.13</v>
+      </c>
+      <c r="F8">
+        <v>132.08000000000001</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>88.049999999999983</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>102227691</v>
+      </c>
+      <c r="B9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" t="s">
+        <v>194</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>402780</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>-30.92</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>-30.92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>7046</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>40</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>301033</v>
+      </c>
+      <c r="B12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D12">
+        <v>131.5</v>
+      </c>
+      <c r="E12">
+        <v>131.5</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>131.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1006090</v>
+      </c>
+      <c r="B13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>-71.06</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>-71.06</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>800000690090</v>
+      </c>
+      <c r="B19" t="s">
+        <v>184</v>
+      </c>
+      <c r="C19" t="s">
+        <v>198</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>288.38</v>
+      </c>
+      <c r="F19">
+        <v>246.58</v>
+      </c>
+      <c r="G19">
+        <f>E19-F19</f>
+        <v>41.799999999999983</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1010006090</v>
+      </c>
+      <c r="B20" t="s">
+        <v>185</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20">
+        <v>491.82</v>
+      </c>
+      <c r="E20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F20" t="s">
+        <v>188</v>
+      </c>
+      <c r="G20" t="e">
+        <f t="shared" ref="G20:G27" si="1">E20-F20</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1010006090</v>
+      </c>
+      <c r="B21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>500</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>800000690090</v>
+      </c>
+      <c r="B22" t="s">
+        <v>203</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>-72.06</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="1"/>
+        <v>-72.06</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>18300690090</v>
+      </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23">
+        <v>184.44</v>
+      </c>
+      <c r="E23">
+        <v>433.9</v>
+      </c>
+      <c r="F23">
+        <v>249.46</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="1"/>
+        <v>184.43999999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>330152984</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24">
+        <v>120.88</v>
+      </c>
+      <c r="E24">
+        <v>208.93</v>
+      </c>
+      <c r="F24">
+        <v>88.05</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="1"/>
+        <v>120.88000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>7046</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25">
+        <v>20</v>
+      </c>
+      <c r="E25">
+        <v>40</v>
+      </c>
+      <c r="F25">
+        <v>20</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>301033</v>
+      </c>
+      <c r="B26" t="s">
+        <v>195</v>
+      </c>
+      <c r="C26" t="s">
+        <v>172</v>
+      </c>
+      <c r="D26">
+        <v>142.75</v>
+      </c>
+      <c r="E26">
+        <v>142.75</v>
+      </c>
+      <c r="F26">
+        <v>131.5</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="1"/>
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>635656766</v>
+      </c>
+      <c r="B27" t="s">
+        <v>204</v>
+      </c>
+      <c r="C27" t="s">
+        <v>205</v>
+      </c>
+      <c r="D27">
+        <v>500</v>
+      </c>
+      <c r="E27">
+        <v>500</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A2:V46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10762,531 +11749,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>800000690090</v>
-      </c>
-      <c r="B2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D2">
-        <v>246.58</v>
-      </c>
-      <c r="E2">
-        <v>669.45</v>
-      </c>
-      <c r="F2">
-        <v>381.07</v>
-      </c>
-      <c r="G2">
-        <f>E2-F2</f>
-        <v>288.38000000000005</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1010006090</v>
-      </c>
-      <c r="B3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E3" t="s">
-        <v>187</v>
-      </c>
-      <c r="F3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G3" t="e">
-        <f t="shared" ref="G3:G13" si="0">E3-F3</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1010006090</v>
-      </c>
-      <c r="B4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" t="s">
-        <v>189</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>190</v>
-      </c>
-      <c r="F4">
-        <v>500</v>
-      </c>
-      <c r="G4" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>18300690090</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5">
-        <v>222.46</v>
-      </c>
-      <c r="E5">
-        <v>495.55</v>
-      </c>
-      <c r="F5">
-        <v>246.09</v>
-      </c>
-      <c r="G5" s="88">
-        <f t="shared" si="0"/>
-        <v>249.46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>18300690090</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D6">
-        <v>222.46</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>8071090</v>
-      </c>
-      <c r="B7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7">
-        <v>498.24</v>
-      </c>
-      <c r="E7">
-        <v>498.24</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="0"/>
-        <v>498.24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>330152984</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8">
-        <v>88.05</v>
-      </c>
-      <c r="E8">
-        <v>220.13</v>
-      </c>
-      <c r="F8">
-        <v>132.08000000000001</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="0"/>
-        <v>88.049999999999983</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>102227691</v>
-      </c>
-      <c r="B9" t="s">
-        <v>193</v>
-      </c>
-      <c r="C9" t="s">
-        <v>194</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>402780</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>-30.92</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="0"/>
-        <v>-30.92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>7046</v>
-      </c>
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11">
-        <v>20</v>
-      </c>
-      <c r="E11">
-        <v>40</v>
-      </c>
-      <c r="F11">
-        <v>20</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>301033</v>
-      </c>
-      <c r="B12" t="s">
-        <v>195</v>
-      </c>
-      <c r="C12" t="s">
-        <v>172</v>
-      </c>
-      <c r="D12">
-        <v>131.5</v>
-      </c>
-      <c r="E12">
-        <v>131.5</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="0"/>
-        <v>131.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>1006090</v>
-      </c>
-      <c r="B13" t="s">
-        <v>196</v>
-      </c>
-      <c r="C13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>-71.06</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="0"/>
-        <v>-71.06</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>800000690090</v>
-      </c>
-      <c r="B19" t="s">
-        <v>184</v>
-      </c>
-      <c r="C19" t="s">
-        <v>198</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>288.38</v>
-      </c>
-      <c r="F19">
-        <v>246.58</v>
-      </c>
-      <c r="G19">
-        <f>E19-F19</f>
-        <v>41.799999999999983</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>1010006090</v>
-      </c>
-      <c r="B20" t="s">
-        <v>185</v>
-      </c>
-      <c r="C20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20">
-        <v>491.82</v>
-      </c>
-      <c r="E20" t="s">
-        <v>202</v>
-      </c>
-      <c r="F20" t="s">
-        <v>188</v>
-      </c>
-      <c r="G20" t="e">
-        <f t="shared" ref="G20:G27" si="1">E20-F20</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>1010006090</v>
-      </c>
-      <c r="B21" t="s">
-        <v>185</v>
-      </c>
-      <c r="C21" t="s">
-        <v>189</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>500</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>800000690090</v>
-      </c>
-      <c r="B22" t="s">
-        <v>203</v>
-      </c>
-      <c r="C22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>-72.06</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="1"/>
-        <v>-72.06</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>18300690090</v>
-      </c>
-      <c r="B23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23">
-        <v>184.44</v>
-      </c>
-      <c r="E23">
-        <v>433.9</v>
-      </c>
-      <c r="F23">
-        <v>249.46</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>184.43999999999997</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>330152984</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24">
-        <v>120.88</v>
-      </c>
-      <c r="E24">
-        <v>208.93</v>
-      </c>
-      <c r="F24">
-        <v>88.05</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="1"/>
-        <v>120.88000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>7046</v>
-      </c>
-      <c r="B25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25">
-        <v>20</v>
-      </c>
-      <c r="E25">
-        <v>40</v>
-      </c>
-      <c r="F25">
-        <v>20</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>301033</v>
-      </c>
-      <c r="B26" t="s">
-        <v>195</v>
-      </c>
-      <c r="C26" t="s">
-        <v>172</v>
-      </c>
-      <c r="D26">
-        <v>142.75</v>
-      </c>
-      <c r="E26">
-        <v>142.75</v>
-      </c>
-      <c r="F26">
-        <v>131.5</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="1"/>
-        <v>11.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>635656766</v>
-      </c>
-      <c r="B27" t="s">
-        <v>204</v>
-      </c>
-      <c r="C27" t="s">
-        <v>205</v>
-      </c>
-      <c r="D27">
-        <v>500</v>
-      </c>
-      <c r="E27">
-        <v>500</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A2:V49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12020,8 +12484,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A2:V48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12734,8 +13198,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A2:V44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13465,8 +13929,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A2:U43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14161,8 +14625,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A2:U38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14796,8 +15260,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A2:U39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -15460,8 +15924,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A2:N32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16224,8 +16688,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A2:N36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16829,8 +17293,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A2:L36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -17409,8 +17873,428 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="B1:L48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="40.85546875" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E1" s="329" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="330"/>
+      <c r="G1" s="330"/>
+      <c r="H1" s="330"/>
+      <c r="I1" s="330"/>
+      <c r="J1" s="330"/>
+      <c r="K1" s="330"/>
+      <c r="L1" s="331"/>
+    </row>
+    <row r="2" spans="2:12" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="130" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="131" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="131" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="131" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="131" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="132" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="131" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="133" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="46">
+        <v>800000530090</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="228" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="153">
+        <v>44</v>
+      </c>
+      <c r="F3" s="153">
+        <v>38</v>
+      </c>
+      <c r="G3" s="224">
+        <f>E3-F3</f>
+        <v>6</v>
+      </c>
+      <c r="H3" s="136">
+        <v>25.224</v>
+      </c>
+      <c r="I3" s="136">
+        <f>G3*H3</f>
+        <v>151.34399999999999</v>
+      </c>
+      <c r="J3" s="241"/>
+      <c r="K3" s="248">
+        <f>I3</f>
+        <v>151.34399999999999</v>
+      </c>
+      <c r="L3" s="238">
+        <f>K3</f>
+        <v>151.34399999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="74">
+        <v>1045012090</v>
+      </c>
+      <c r="C4" s="74" t="s">
+        <v>225</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="46">
+        <f t="shared" ref="G4:G5" si="0">E4-F4</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="74"/>
+      <c r="I4" s="48">
+        <f t="shared" ref="I4" si="1">G4*H4</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="242"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="250">
+        <f t="shared" ref="L4:L12" si="2">K4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="46">
+        <v>18300530090</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="228" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="226"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="46">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="48"/>
+      <c r="I5" s="227">
+        <v>229.55</v>
+      </c>
+      <c r="J5" s="243"/>
+      <c r="K5" s="251">
+        <v>151.78</v>
+      </c>
+      <c r="L5" s="250">
+        <f t="shared" si="2"/>
+        <v>151.78</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B6" s="46">
+        <v>8216090</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="D6" s="228" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="152"/>
+      <c r="F6" s="152"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="48">
+        <v>0.9</v>
+      </c>
+      <c r="I6" s="48">
+        <f t="shared" ref="I6:I11" si="3">G6*H6</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="244">
+        <f>I6+I7</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="252">
+        <f>J6</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="250">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B7" s="46"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="228"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="48">
+        <v>1.68</v>
+      </c>
+      <c r="I7" s="48">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="245"/>
+      <c r="K7" s="253"/>
+      <c r="L7" s="250">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="46">
+        <v>414035</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="228" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="46">
+        <f t="shared" ref="G8:G11" si="4">E8-F8</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="48">
+        <v>1.68</v>
+      </c>
+      <c r="I8" s="48">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="245"/>
+      <c r="K8" s="253"/>
+      <c r="L8" s="250">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B9" s="46">
+        <v>7046</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="228" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="48">
+        <v>1.68</v>
+      </c>
+      <c r="I9" s="48">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="245"/>
+      <c r="K9" s="254">
+        <v>21.14</v>
+      </c>
+      <c r="L9" s="250">
+        <f t="shared" si="2"/>
+        <v>21.14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="46">
+        <v>21502</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="228" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="48">
+        <v>1.68</v>
+      </c>
+      <c r="I10" s="48">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="245"/>
+      <c r="K10" s="255"/>
+      <c r="L10" s="250">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="46">
+        <v>330157218</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="228" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="152">
+        <v>273</v>
+      </c>
+      <c r="F11" s="152">
+        <v>267</v>
+      </c>
+      <c r="G11" s="46">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="H11" s="48">
+        <v>4.3260719999999999</v>
+      </c>
+      <c r="I11" s="48">
+        <f t="shared" si="3"/>
+        <v>25.956432</v>
+      </c>
+      <c r="J11" s="245"/>
+      <c r="K11" s="254">
+        <v>25.36</v>
+      </c>
+      <c r="L11" s="250">
+        <f t="shared" si="2"/>
+        <v>25.36</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="229">
+        <v>330157218</v>
+      </c>
+      <c r="C12" s="229" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="228"/>
+      <c r="E12" s="175"/>
+      <c r="F12" s="175"/>
+      <c r="G12" s="165"/>
+      <c r="H12" s="166"/>
+      <c r="I12" s="166"/>
+      <c r="J12" s="246"/>
+      <c r="K12" s="254">
+        <v>0.88</v>
+      </c>
+      <c r="L12" s="250">
+        <f t="shared" si="2"/>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="46"/>
+      <c r="C13" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="228"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="247"/>
+      <c r="K13" s="256">
+        <v>0</v>
+      </c>
+      <c r="L13" s="259">
+        <f>K13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="74"/>
+      <c r="C14" s="47" t="s">
+        <v>208</v>
+      </c>
+      <c r="K14" s="257"/>
+      <c r="L14" s="258">
+        <f>SUM(L3:L13)</f>
+        <v>350.50400000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D46" s="114">
+        <v>5.2679999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D47" s="114">
+        <v>5.82</v>
+      </c>
+    </row>
+    <row r="48" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D48">
+        <f>SUM(D46:D47)</f>
+        <v>11.088000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A2:L35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -17976,428 +18860,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:L48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="40.85546875" customWidth="1"/>
-    <col min="4" max="4" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="17.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E1" s="329" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="330"/>
-      <c r="G1" s="330"/>
-      <c r="H1" s="330"/>
-      <c r="I1" s="330"/>
-      <c r="J1" s="330"/>
-      <c r="K1" s="330"/>
-      <c r="L1" s="331"/>
-    </row>
-    <row r="2" spans="2:12" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="130" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" s="131" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="131" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="131" t="s">
-        <v>47</v>
-      </c>
-      <c r="I2" s="131" t="s">
-        <v>48</v>
-      </c>
-      <c r="J2" s="132" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="131" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" s="133" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="46">
-        <v>800000530090</v>
-      </c>
-      <c r="C3" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="D3" s="228" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="153">
-        <v>44</v>
-      </c>
-      <c r="F3" s="153">
-        <v>38</v>
-      </c>
-      <c r="G3" s="224">
-        <f>E3-F3</f>
-        <v>6</v>
-      </c>
-      <c r="H3" s="136">
-        <v>25.224</v>
-      </c>
-      <c r="I3" s="136">
-        <f>G3*H3</f>
-        <v>151.34399999999999</v>
-      </c>
-      <c r="J3" s="241"/>
-      <c r="K3" s="248">
-        <f>I3</f>
-        <v>151.34399999999999</v>
-      </c>
-      <c r="L3" s="238">
-        <f>K3</f>
-        <v>151.34399999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="74">
-        <v>1045012090</v>
-      </c>
-      <c r="C4" s="74" t="s">
-        <v>225</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="46">
-        <f t="shared" ref="G4:G5" si="0">E4-F4</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="74"/>
-      <c r="I4" s="48">
-        <f t="shared" ref="I4" si="1">G4*H4</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="242"/>
-      <c r="K4" s="249"/>
-      <c r="L4" s="250">
-        <f t="shared" ref="L4:L12" si="2">K4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="46">
-        <v>18300530090</v>
-      </c>
-      <c r="C5" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="228" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="226"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="46">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="48"/>
-      <c r="I5" s="227">
-        <v>229.55</v>
-      </c>
-      <c r="J5" s="243"/>
-      <c r="K5" s="251">
-        <v>151.78</v>
-      </c>
-      <c r="L5" s="250">
-        <f t="shared" si="2"/>
-        <v>151.78</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="B6" s="46">
-        <v>8216090</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="D6" s="228" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="152"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="48">
-        <v>0.9</v>
-      </c>
-      <c r="I6" s="48">
-        <f t="shared" ref="I6:I11" si="3">G6*H6</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="244">
-        <f>I6+I7</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="252">
-        <f>J6</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="250">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="46"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="228"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="48">
-        <v>1.68</v>
-      </c>
-      <c r="I7" s="48">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="245"/>
-      <c r="K7" s="253"/>
-      <c r="L7" s="250">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="46">
-        <v>414035</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="228" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="46">
-        <f t="shared" ref="G8:G11" si="4">E8-F8</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="48">
-        <v>1.68</v>
-      </c>
-      <c r="I8" s="48">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="245"/>
-      <c r="K8" s="253"/>
-      <c r="L8" s="250">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="46">
-        <v>7046</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="228" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="46">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="48">
-        <v>1.68</v>
-      </c>
-      <c r="I9" s="48">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="245"/>
-      <c r="K9" s="254">
-        <v>21.14</v>
-      </c>
-      <c r="L9" s="250">
-        <f t="shared" si="2"/>
-        <v>21.14</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="46">
-        <v>21502</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="228" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="46">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="48">
-        <v>1.68</v>
-      </c>
-      <c r="I10" s="48">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="245"/>
-      <c r="K10" s="255"/>
-      <c r="L10" s="250">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="46">
-        <v>330157218</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="228" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="152">
-        <v>273</v>
-      </c>
-      <c r="F11" s="152">
-        <v>267</v>
-      </c>
-      <c r="G11" s="46">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="H11" s="48">
-        <v>4.3260719999999999</v>
-      </c>
-      <c r="I11" s="48">
-        <f t="shared" si="3"/>
-        <v>25.956432</v>
-      </c>
-      <c r="J11" s="245"/>
-      <c r="K11" s="254">
-        <v>25.36</v>
-      </c>
-      <c r="L11" s="250">
-        <f t="shared" si="2"/>
-        <v>25.36</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="229">
-        <v>330157218</v>
-      </c>
-      <c r="C12" s="229" t="s">
-        <v>226</v>
-      </c>
-      <c r="D12" s="228"/>
-      <c r="E12" s="175"/>
-      <c r="F12" s="175"/>
-      <c r="G12" s="165"/>
-      <c r="H12" s="166"/>
-      <c r="I12" s="166"/>
-      <c r="J12" s="246"/>
-      <c r="K12" s="254">
-        <v>0.88</v>
-      </c>
-      <c r="L12" s="250">
-        <f t="shared" si="2"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="46"/>
-      <c r="C13" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="228"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="247"/>
-      <c r="K13" s="256">
-        <v>0</v>
-      </c>
-      <c r="L13" s="259">
-        <f>K13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="74"/>
-      <c r="C14" s="47" t="s">
-        <v>208</v>
-      </c>
-      <c r="K14" s="257"/>
-      <c r="L14" s="258">
-        <f>SUM(L3:L13)</f>
-        <v>350.50400000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D46" s="114">
-        <v>5.2679999999999998</v>
-      </c>
-    </row>
-    <row r="47" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D47" s="114">
-        <v>5.82</v>
-      </c>
-    </row>
-    <row r="48" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D48">
-        <f>SUM(D46:D47)</f>
-        <v>11.088000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="E1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A2:J31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18889,8 +19353,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A2:J30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19342,8 +19806,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A2:E30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19738,8 +20202,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A2:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20144,8 +20608,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A2:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20526,8 +20990,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -20536,8 +21000,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:ZD52"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B1:ZM52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.140625" customWidth="1"/>
@@ -20907,9 +21371,11 @@
     <col min="677" max="677" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="679" max="679" width="13.28515625" customWidth="1"/>
     <col min="680" max="680" width="16.42578125" customWidth="1"/>
+    <col min="687" max="687" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="689" max="689" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:680" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:689" x14ac:dyDescent="0.25">
       <c r="E1" s="329" t="s">
         <v>54</v>
       </c>
@@ -21720,8 +22186,18 @@
       <c r="ZB1" s="330"/>
       <c r="ZC1" s="330"/>
       <c r="ZD1" s="331"/>
-    </row>
-    <row r="2" spans="2:680" ht="270.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="ZF1" s="332">
+        <v>45413</v>
+      </c>
+      <c r="ZG1" s="330"/>
+      <c r="ZH1" s="330"/>
+      <c r="ZI1" s="330"/>
+      <c r="ZJ1" s="330"/>
+      <c r="ZK1" s="330"/>
+      <c r="ZL1" s="330"/>
+      <c r="ZM1" s="331"/>
+    </row>
+    <row r="2" spans="2:689" ht="270.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="45" t="s">
         <v>42</v>
       </c>
@@ -23675,8 +24151,32 @@
       <c r="ZD2" s="133" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="2:680" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="ZF2" s="130" t="s">
+        <v>44</v>
+      </c>
+      <c r="ZG2" s="131" t="s">
+        <v>45</v>
+      </c>
+      <c r="ZH2" s="131" t="s">
+        <v>46</v>
+      </c>
+      <c r="ZI2" s="131" t="s">
+        <v>47</v>
+      </c>
+      <c r="ZJ2" s="131" t="s">
+        <v>48</v>
+      </c>
+      <c r="ZK2" s="132" t="s">
+        <v>25</v>
+      </c>
+      <c r="ZL2" s="131" t="s">
+        <v>43</v>
+      </c>
+      <c r="ZM2" s="133" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="2:689" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="46">
         <v>800000690090</v>
       </c>
@@ -25791,8 +26291,34 @@
         <f>ZC3</f>
         <v>501.88799999999998</v>
       </c>
-    </row>
-    <row r="4" spans="2:680" x14ac:dyDescent="0.25">
+      <c r="ZF3" s="279">
+        <v>984</v>
+      </c>
+      <c r="ZG3" s="279">
+        <v>972</v>
+      </c>
+      <c r="ZH3" s="135">
+        <f>ZF3-ZG3</f>
+        <v>12</v>
+      </c>
+      <c r="ZI3" s="136">
+        <v>31.367999999999999</v>
+      </c>
+      <c r="ZJ3" s="136">
+        <f>ZH3*ZI3</f>
+        <v>376.416</v>
+      </c>
+      <c r="ZK3" s="137"/>
+      <c r="ZL3" s="315">
+        <f>ZJ3+ZJ4</f>
+        <v>533.25599999999997</v>
+      </c>
+      <c r="ZM3" s="322">
+        <f>ZL3</f>
+        <v>533.25599999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="2:689" x14ac:dyDescent="0.25">
       <c r="B4" s="46"/>
       <c r="C4" s="47" t="s">
         <v>53</v>
@@ -27741,8 +28267,32 @@
       <c r="ZD4" s="323">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="2:680" ht="30" x14ac:dyDescent="0.25">
+      <c r="ZF4" s="280">
+        <v>533</v>
+      </c>
+      <c r="ZG4" s="280">
+        <v>528</v>
+      </c>
+      <c r="ZH4" s="46">
+        <f>ZF4-ZG4</f>
+        <v>5</v>
+      </c>
+      <c r="ZI4" s="48">
+        <v>31.367999999999999</v>
+      </c>
+      <c r="ZJ4" s="48">
+        <f>ZH4*ZI4</f>
+        <v>156.84</v>
+      </c>
+      <c r="ZK4" s="49"/>
+      <c r="ZL4" s="306" t="s">
+        <v>118</v>
+      </c>
+      <c r="ZM4" s="323">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="2:689" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="74">
         <v>1010006090</v>
       </c>
@@ -29183,8 +29733,27 @@
         <f>ZC5</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="2:680" x14ac:dyDescent="0.25">
+      <c r="ZF5" s="281"/>
+      <c r="ZG5" s="281"/>
+      <c r="ZH5" s="46">
+        <f t="shared" ref="ZH5" si="142">ZF5-ZG5</f>
+        <v>0</v>
+      </c>
+      <c r="ZI5" s="74"/>
+      <c r="ZJ5" s="48">
+        <f t="shared" ref="ZJ5" si="143">ZH5*ZI5</f>
+        <v>0</v>
+      </c>
+      <c r="ZK5" s="179"/>
+      <c r="ZL5" s="195">
+        <v>0</v>
+      </c>
+      <c r="ZM5" s="319">
+        <f>ZL5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:689" x14ac:dyDescent="0.25">
       <c r="B6" s="74">
         <v>1010006090</v>
       </c>
@@ -29938,8 +30507,20 @@
       <c r="ZD6" s="323">
         <v>8.34</v>
       </c>
-    </row>
-    <row r="7" spans="2:680" x14ac:dyDescent="0.25">
+      <c r="ZF6" s="281"/>
+      <c r="ZG6" s="281"/>
+      <c r="ZH6" s="46"/>
+      <c r="ZI6" s="74"/>
+      <c r="ZJ6" s="48"/>
+      <c r="ZK6" s="179"/>
+      <c r="ZL6" s="195">
+        <v>0</v>
+      </c>
+      <c r="ZM6" s="323">
+        <v>8.34</v>
+      </c>
+    </row>
+    <row r="7" spans="2:689" x14ac:dyDescent="0.25">
       <c r="B7" s="46">
         <v>18300690090</v>
       </c>
@@ -30061,7 +30642,7 @@
         <v>166.14</v>
       </c>
       <c r="AZ7" s="99">
-        <f t="shared" ref="AZ7:AZ17" si="142">AY7</f>
+        <f t="shared" ref="AZ7:AZ17" si="144">AY7</f>
         <v>166.14</v>
       </c>
       <c r="BA7" s="67"/>
@@ -30083,7 +30664,7 @@
         <v>260.38</v>
       </c>
       <c r="BH7" s="99">
-        <f t="shared" ref="BH7:BH17" si="143">BG7</f>
+        <f t="shared" ref="BH7:BH17" si="145">BG7</f>
         <v>260.38</v>
       </c>
       <c r="BI7" s="67"/>
@@ -30105,7 +30686,7 @@
         <v>242.38</v>
       </c>
       <c r="BP7" s="99">
-        <f t="shared" ref="BP7:BP17" si="144">BO7</f>
+        <f t="shared" ref="BP7:BP17" si="146">BO7</f>
         <v>242.38</v>
       </c>
       <c r="BQ7" s="67"/>
@@ -30976,7 +31557,7 @@
       <c r="QP7" s="278"/>
       <c r="QQ7" s="278"/>
       <c r="QR7" s="46">
-        <f t="shared" ref="QR7" si="145">QP7-QQ7</f>
+        <f t="shared" ref="QR7" si="147">QP7-QQ7</f>
         <v>0</v>
       </c>
       <c r="QS7" s="48"/>
@@ -30990,7 +31571,7 @@
       <c r="QX7" s="278"/>
       <c r="QY7" s="278"/>
       <c r="QZ7" s="46">
-        <f t="shared" ref="QZ7" si="146">QX7-QY7</f>
+        <f t="shared" ref="QZ7" si="148">QX7-QY7</f>
         <v>0</v>
       </c>
       <c r="RA7" s="48"/>
@@ -31004,7 +31585,7 @@
       <c r="RG7" s="278"/>
       <c r="RH7" s="278"/>
       <c r="RI7" s="46">
-        <f t="shared" ref="RI7" si="147">RG7-RH7</f>
+        <f t="shared" ref="RI7" si="149">RG7-RH7</f>
         <v>0</v>
       </c>
       <c r="RJ7" s="48"/>
@@ -31018,7 +31599,7 @@
       <c r="RP7" s="278"/>
       <c r="RQ7" s="278"/>
       <c r="RR7" s="46">
-        <f t="shared" ref="RR7" si="148">RP7-RQ7</f>
+        <f t="shared" ref="RR7" si="150">RP7-RQ7</f>
         <v>0</v>
       </c>
       <c r="RS7" s="48"/>
@@ -31032,7 +31613,7 @@
       <c r="RY7" s="278"/>
       <c r="RZ7" s="278"/>
       <c r="SA7" s="46">
-        <f t="shared" ref="SA7" si="149">RY7-RZ7</f>
+        <f t="shared" ref="SA7" si="151">RY7-RZ7</f>
         <v>0</v>
       </c>
       <c r="SB7" s="48"/>
@@ -31046,7 +31627,7 @@
       <c r="SH7" s="278"/>
       <c r="SI7" s="278"/>
       <c r="SJ7" s="46">
-        <f t="shared" ref="SJ7" si="150">SH7-SI7</f>
+        <f t="shared" ref="SJ7" si="152">SH7-SI7</f>
         <v>0</v>
       </c>
       <c r="SK7" s="48"/>
@@ -31060,7 +31641,7 @@
       <c r="SQ7" s="278"/>
       <c r="SR7" s="278"/>
       <c r="SS7" s="46">
-        <f t="shared" ref="SS7" si="151">SQ7-SR7</f>
+        <f t="shared" ref="SS7" si="153">SQ7-SR7</f>
         <v>0</v>
       </c>
       <c r="ST7" s="48"/>
@@ -31074,7 +31655,7 @@
       <c r="SZ7" s="278"/>
       <c r="TA7" s="278"/>
       <c r="TB7" s="46">
-        <f t="shared" ref="TB7" si="152">SZ7-TA7</f>
+        <f t="shared" ref="TB7" si="154">SZ7-TA7</f>
         <v>0</v>
       </c>
       <c r="TC7" s="48"/>
@@ -31088,7 +31669,7 @@
       <c r="TI7" s="278"/>
       <c r="TJ7" s="310"/>
       <c r="TK7" s="46">
-        <f t="shared" ref="TK7" si="153">TI7-TJ7</f>
+        <f t="shared" ref="TK7" si="155">TI7-TJ7</f>
         <v>0</v>
       </c>
       <c r="TL7" s="48"/>
@@ -31102,7 +31683,7 @@
       <c r="TR7" s="278"/>
       <c r="TS7" s="310"/>
       <c r="TT7" s="46">
-        <f t="shared" ref="TT7" si="154">TR7-TS7</f>
+        <f t="shared" ref="TT7" si="156">TR7-TS7</f>
         <v>0</v>
       </c>
       <c r="TU7" s="48"/>
@@ -31116,7 +31697,7 @@
       <c r="UA7" s="278"/>
       <c r="UB7" s="310"/>
       <c r="UC7" s="46">
-        <f t="shared" ref="UC7" si="155">UA7-UB7</f>
+        <f t="shared" ref="UC7" si="157">UA7-UB7</f>
         <v>0</v>
       </c>
       <c r="UD7" s="48"/>
@@ -31130,7 +31711,7 @@
       <c r="UJ7" s="278"/>
       <c r="UK7" s="310"/>
       <c r="UL7" s="46">
-        <f t="shared" ref="UL7" si="156">UJ7-UK7</f>
+        <f t="shared" ref="UL7" si="158">UJ7-UK7</f>
         <v>0</v>
       </c>
       <c r="UM7" s="48"/>
@@ -31144,7 +31725,7 @@
       <c r="US7" s="278"/>
       <c r="UT7" s="310"/>
       <c r="UU7" s="46">
-        <f t="shared" ref="UU7" si="157">US7-UT7</f>
+        <f t="shared" ref="UU7" si="159">US7-UT7</f>
         <v>0</v>
       </c>
       <c r="UV7" s="48"/>
@@ -31158,7 +31739,7 @@
       <c r="VB7" s="278"/>
       <c r="VC7" s="310"/>
       <c r="VD7" s="46">
-        <f t="shared" ref="VD7" si="158">VB7-VC7</f>
+        <f t="shared" ref="VD7" si="160">VB7-VC7</f>
         <v>0</v>
       </c>
       <c r="VE7" s="48"/>
@@ -31172,7 +31753,7 @@
       <c r="VK7" s="278"/>
       <c r="VL7" s="278"/>
       <c r="VM7" s="46">
-        <f t="shared" ref="VM7" si="159">VK7-VL7</f>
+        <f t="shared" ref="VM7" si="161">VK7-VL7</f>
         <v>0</v>
       </c>
       <c r="VN7" s="48"/>
@@ -31186,7 +31767,7 @@
       <c r="VT7" s="278"/>
       <c r="VU7" s="278"/>
       <c r="VV7" s="46">
-        <f t="shared" ref="VV7" si="160">VT7-VU7</f>
+        <f t="shared" ref="VV7" si="162">VT7-VU7</f>
         <v>0</v>
       </c>
       <c r="VW7" s="48"/>
@@ -31200,7 +31781,7 @@
       <c r="WC7" s="278"/>
       <c r="WD7" s="278"/>
       <c r="WE7" s="46">
-        <f t="shared" ref="WE7" si="161">WC7-WD7</f>
+        <f t="shared" ref="WE7" si="163">WC7-WD7</f>
         <v>0</v>
       </c>
       <c r="WF7" s="48"/>
@@ -31214,7 +31795,7 @@
       <c r="WL7" s="278"/>
       <c r="WM7" s="278"/>
       <c r="WN7" s="46">
-        <f t="shared" ref="WN7" si="162">WL7-WM7</f>
+        <f t="shared" ref="WN7" si="164">WL7-WM7</f>
         <v>0</v>
       </c>
       <c r="WO7" s="48"/>
@@ -31228,7 +31809,7 @@
       <c r="WU7" s="278"/>
       <c r="WV7" s="278"/>
       <c r="WW7" s="46">
-        <f t="shared" ref="WW7" si="163">WU7-WV7</f>
+        <f t="shared" ref="WW7" si="165">WU7-WV7</f>
         <v>0</v>
       </c>
       <c r="WX7" s="48"/>
@@ -31242,7 +31823,7 @@
       <c r="XD7" s="278"/>
       <c r="XE7" s="278"/>
       <c r="XF7" s="46">
-        <f t="shared" ref="XF7" si="164">XD7-XE7</f>
+        <f t="shared" ref="XF7" si="166">XD7-XE7</f>
         <v>0</v>
       </c>
       <c r="XG7" s="48"/>
@@ -31256,7 +31837,7 @@
       <c r="XM7" s="278"/>
       <c r="XN7" s="278"/>
       <c r="XO7" s="46">
-        <f t="shared" ref="XO7" si="165">XM7-XN7</f>
+        <f t="shared" ref="XO7" si="167">XM7-XN7</f>
         <v>0</v>
       </c>
       <c r="XP7" s="48"/>
@@ -31270,7 +31851,7 @@
       <c r="XV7" s="278"/>
       <c r="XW7" s="278"/>
       <c r="XX7" s="46">
-        <f t="shared" ref="XX7" si="166">XV7-XW7</f>
+        <f t="shared" ref="XX7" si="168">XV7-XW7</f>
         <v>0</v>
       </c>
       <c r="XY7" s="48"/>
@@ -31284,7 +31865,7 @@
       <c r="YE7" s="278"/>
       <c r="YF7" s="278"/>
       <c r="YG7" s="46">
-        <f t="shared" ref="YG7" si="167">YE7-YF7</f>
+        <f t="shared" ref="YG7" si="169">YE7-YF7</f>
         <v>0</v>
       </c>
       <c r="YH7" s="48"/>
@@ -31298,7 +31879,7 @@
       <c r="YN7" s="278"/>
       <c r="YO7" s="278"/>
       <c r="YP7" s="46">
-        <f t="shared" ref="YP7" si="168">YN7-YO7</f>
+        <f t="shared" ref="YP7" si="170">YN7-YO7</f>
         <v>0</v>
       </c>
       <c r="YQ7" s="48"/>
@@ -31312,7 +31893,7 @@
       <c r="YW7" s="278"/>
       <c r="YX7" s="278"/>
       <c r="YY7" s="46">
-        <f t="shared" ref="YY7" si="169">YW7-YX7</f>
+        <f t="shared" ref="YY7" si="171">YW7-YX7</f>
         <v>0</v>
       </c>
       <c r="YZ7" s="48"/>
@@ -31323,8 +31904,22 @@
         <v>0</v>
       </c>
       <c r="ZD7" s="75"/>
-    </row>
-    <row r="8" spans="2:680" x14ac:dyDescent="0.25">
+      <c r="ZF7" s="278"/>
+      <c r="ZG7" s="278"/>
+      <c r="ZH7" s="46">
+        <f t="shared" ref="ZH7" si="172">ZF7-ZG7</f>
+        <v>0</v>
+      </c>
+      <c r="ZI7" s="48"/>
+      <c r="ZJ7" s="311"/>
+      <c r="ZK7" s="312"/>
+      <c r="ZL7" s="306">
+        <f>ZK7</f>
+        <v>0</v>
+      </c>
+      <c r="ZM7" s="75"/>
+    </row>
+    <row r="8" spans="2:689" x14ac:dyDescent="0.25">
       <c r="B8" s="46">
         <v>18300690090</v>
       </c>
@@ -32111,8 +32706,20 @@
       <c r="ZD8" s="323">
         <v>451.5</v>
       </c>
-    </row>
-    <row r="9" spans="2:680" x14ac:dyDescent="0.25">
+      <c r="ZF8" s="278"/>
+      <c r="ZG8" s="278"/>
+      <c r="ZH8" s="46"/>
+      <c r="ZI8" s="48"/>
+      <c r="ZJ8" s="311"/>
+      <c r="ZK8" s="312"/>
+      <c r="ZL8" s="307">
+        <v>451.5</v>
+      </c>
+      <c r="ZM8" s="323">
+        <v>451.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:689" x14ac:dyDescent="0.25">
       <c r="B9" s="46">
         <v>8071090</v>
       </c>
@@ -32257,7 +32864,7 @@
         <v>731.34</v>
       </c>
       <c r="AZ9" s="99">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>731.34</v>
       </c>
       <c r="BA9" s="76">
@@ -32284,7 +32891,7 @@
         <v>570.20000000000005</v>
       </c>
       <c r="BH9" s="99">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>570.20000000000005</v>
       </c>
       <c r="BI9" s="76">
@@ -32311,7 +32918,7 @@
         <v>795.6</v>
       </c>
       <c r="BP9" s="99">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>795.6</v>
       </c>
       <c r="BQ9" s="76">
@@ -32704,7 +33311,7 @@
         <v>0.9</v>
       </c>
       <c r="GE9" s="48">
-        <f t="shared" ref="GE9:GE14" si="170">GC9*GD9</f>
+        <f t="shared" ref="GE9:GE14" si="173">GC9*GD9</f>
         <v>90</v>
       </c>
       <c r="GF9" s="98">
@@ -32728,7 +33335,7 @@
         <v>0.9</v>
       </c>
       <c r="GM9" s="48">
-        <f t="shared" ref="GM9:GM14" si="171">GK9*GL9</f>
+        <f t="shared" ref="GM9:GM14" si="174">GK9*GL9</f>
         <v>90</v>
       </c>
       <c r="GN9" s="98">
@@ -32750,7 +33357,7 @@
         <v>0.9</v>
       </c>
       <c r="GU9" s="48">
-        <f t="shared" ref="GU9:GU14" si="172">GS9*GT9</f>
+        <f t="shared" ref="GU9:GU14" si="175">GS9*GT9</f>
         <v>90</v>
       </c>
       <c r="GV9" s="98">
@@ -32777,7 +33384,7 @@
         <v>0.9</v>
       </c>
       <c r="HC9" s="48">
-        <f t="shared" ref="HC9:HC14" si="173">HA9*HB9</f>
+        <f t="shared" ref="HC9:HC14" si="176">HA9*HB9</f>
         <v>90</v>
       </c>
       <c r="HD9" s="98">
@@ -32804,7 +33411,7 @@
         <v>0.9</v>
       </c>
       <c r="HK9" s="48">
-        <f t="shared" ref="HK9:HK14" si="174">HI9*HJ9</f>
+        <f t="shared" ref="HK9:HK14" si="177">HI9*HJ9</f>
         <v>90</v>
       </c>
       <c r="HL9" s="98">
@@ -32828,7 +33435,7 @@
         <v>0.9</v>
       </c>
       <c r="HS9" s="48">
-        <f t="shared" ref="HS9:HS14" si="175">HQ9*HR9</f>
+        <f t="shared" ref="HS9:HS14" si="178">HQ9*HR9</f>
         <v>90</v>
       </c>
       <c r="HT9" s="98">
@@ -32856,7 +33463,7 @@
         <v>0.9</v>
       </c>
       <c r="IA9" s="48">
-        <f t="shared" ref="IA9:IA14" si="176">HY9*HZ9</f>
+        <f t="shared" ref="IA9:IA14" si="179">HY9*HZ9</f>
         <v>90</v>
       </c>
       <c r="IB9" s="98">
@@ -32884,7 +33491,7 @@
         <v>0.9</v>
       </c>
       <c r="II9" s="48">
-        <f t="shared" ref="II9:II14" si="177">IG9*IH9</f>
+        <f t="shared" ref="II9:II14" si="180">IG9*IH9</f>
         <v>90</v>
       </c>
       <c r="IJ9" s="98">
@@ -32912,7 +33519,7 @@
         <v>0.9</v>
       </c>
       <c r="IQ9" s="48">
-        <f t="shared" ref="IQ9:IQ14" si="178">IO9*IP9</f>
+        <f t="shared" ref="IQ9:IQ14" si="181">IO9*IP9</f>
         <v>90</v>
       </c>
       <c r="IR9" s="98">
@@ -32940,7 +33547,7 @@
         <v>0.9</v>
       </c>
       <c r="IY9" s="48">
-        <f t="shared" ref="IY9:IY14" si="179">IW9*IX9</f>
+        <f t="shared" ref="IY9:IY14" si="182">IW9*IX9</f>
         <v>90</v>
       </c>
       <c r="IZ9" s="98">
@@ -32968,7 +33575,7 @@
         <v>0.9</v>
       </c>
       <c r="JG9" s="48">
-        <f t="shared" ref="JG9:JG14" si="180">JE9*JF9</f>
+        <f t="shared" ref="JG9:JG14" si="183">JE9*JF9</f>
         <v>90</v>
       </c>
       <c r="JH9" s="98">
@@ -32996,7 +33603,7 @@
         <v>0.9</v>
       </c>
       <c r="JO9" s="48">
-        <f t="shared" ref="JO9:JO14" si="181">JM9*JN9</f>
+        <f t="shared" ref="JO9:JO14" si="184">JM9*JN9</f>
         <v>90</v>
       </c>
       <c r="JP9" s="98">
@@ -33024,7 +33631,7 @@
         <v>0.9</v>
       </c>
       <c r="JW9" s="48">
-        <f t="shared" ref="JW9:JW14" si="182">JU9*JV9</f>
+        <f t="shared" ref="JW9:JW14" si="185">JU9*JV9</f>
         <v>90</v>
       </c>
       <c r="JX9" s="98">
@@ -33052,7 +33659,7 @@
         <v>0.9</v>
       </c>
       <c r="KE9" s="48">
-        <f t="shared" ref="KE9:KE14" si="183">KC9*KD9</f>
+        <f t="shared" ref="KE9:KE14" si="186">KC9*KD9</f>
         <v>90</v>
       </c>
       <c r="KF9" s="98">
@@ -33080,7 +33687,7 @@
         <v>0.9</v>
       </c>
       <c r="KM9" s="48">
-        <f t="shared" ref="KM9:KM14" si="184">KK9*KL9</f>
+        <f t="shared" ref="KM9:KM14" si="187">KK9*KL9</f>
         <v>90</v>
       </c>
       <c r="KN9" s="98">
@@ -33108,7 +33715,7 @@
         <v>0.9</v>
       </c>
       <c r="KU9" s="48">
-        <f t="shared" ref="KU9:KU14" si="185">KS9*KT9</f>
+        <f t="shared" ref="KU9:KU14" si="188">KS9*KT9</f>
         <v>90</v>
       </c>
       <c r="KV9" s="98">
@@ -33136,7 +33743,7 @@
         <v>0.9</v>
       </c>
       <c r="LC9" s="48">
-        <f t="shared" ref="LC9:LC14" si="186">LA9*LB9</f>
+        <f t="shared" ref="LC9:LC14" si="189">LA9*LB9</f>
         <v>90</v>
       </c>
       <c r="LD9" s="98">
@@ -33163,7 +33770,7 @@
         <v>0.9</v>
       </c>
       <c r="LK9" s="48">
-        <f t="shared" ref="LK9:LK14" si="187">LI9*LJ9</f>
+        <f t="shared" ref="LK9:LK14" si="190">LI9*LJ9</f>
         <v>90</v>
       </c>
       <c r="LL9" s="98">
@@ -33191,7 +33798,7 @@
         <v>0.9</v>
       </c>
       <c r="LS9" s="48">
-        <f t="shared" ref="LS9" si="188">LQ9*LR9</f>
+        <f t="shared" ref="LS9" si="191">LQ9*LR9</f>
         <v>90</v>
       </c>
       <c r="LT9" s="98">
@@ -33219,7 +33826,7 @@
         <v>0.9</v>
       </c>
       <c r="MA9" s="48">
-        <f t="shared" ref="MA9" si="189">LY9*LZ9</f>
+        <f t="shared" ref="MA9" si="192">LY9*LZ9</f>
         <v>90</v>
       </c>
       <c r="MB9" s="98">
@@ -33248,7 +33855,7 @@
         <v>1.68</v>
       </c>
       <c r="MJ9" s="48">
-        <f t="shared" ref="MJ9" si="190">MH9*MI9</f>
+        <f t="shared" ref="MJ9" si="193">MH9*MI9</f>
         <v>967.68</v>
       </c>
       <c r="MK9" s="98">
@@ -33277,7 +33884,7 @@
         <v>1.68</v>
       </c>
       <c r="MR9" s="48">
-        <f t="shared" ref="MR9" si="191">MP9*MQ9</f>
+        <f t="shared" ref="MR9" si="194">MP9*MQ9</f>
         <v>787.92</v>
       </c>
       <c r="MS9" s="98">
@@ -33306,7 +33913,7 @@
         <v>1.68</v>
       </c>
       <c r="MZ9" s="48">
-        <f t="shared" ref="MZ9" si="192">MX9*MY9</f>
+        <f t="shared" ref="MZ9" si="195">MX9*MY9</f>
         <v>907.19999999999993</v>
       </c>
       <c r="NA9" s="98">
@@ -33335,7 +33942,7 @@
         <v>1.68</v>
       </c>
       <c r="NH9" s="48">
-        <f t="shared" ref="NH9" si="193">NF9*NG9</f>
+        <f t="shared" ref="NH9" si="196">NF9*NG9</f>
         <v>712.31999999999994</v>
       </c>
       <c r="NI9" s="98">
@@ -33364,7 +33971,7 @@
         <v>1.68</v>
       </c>
       <c r="NP9" s="48">
-        <f t="shared" ref="NP9" si="194">NN9*NO9</f>
+        <f t="shared" ref="NP9" si="197">NN9*NO9</f>
         <v>779.52</v>
       </c>
       <c r="NQ9" s="98">
@@ -33393,7 +34000,7 @@
         <v>1.68</v>
       </c>
       <c r="NX9" s="48">
-        <f t="shared" ref="NX9" si="195">NV9*NW9</f>
+        <f t="shared" ref="NX9" si="198">NV9*NW9</f>
         <v>1286.8799999999999</v>
       </c>
       <c r="NY9" s="98">
@@ -33422,7 +34029,7 @@
         <v>1.68</v>
       </c>
       <c r="OF9" s="48">
-        <f t="shared" ref="OF9" si="196">OD9*OE9</f>
+        <f t="shared" ref="OF9" si="199">OD9*OE9</f>
         <v>749.28</v>
       </c>
       <c r="OG9" s="98">
@@ -33451,7 +34058,7 @@
         <v>1.68</v>
       </c>
       <c r="ON9" s="48">
-        <f t="shared" ref="ON9" si="197">OL9*OM9</f>
+        <f t="shared" ref="ON9" si="200">OL9*OM9</f>
         <v>588</v>
       </c>
       <c r="OO9" s="98">
@@ -33479,7 +34086,7 @@
         <v>1.44</v>
       </c>
       <c r="OV9" s="48">
-        <f t="shared" ref="OV9" si="198">OT9*OU9</f>
+        <f t="shared" ref="OV9" si="201">OT9*OU9</f>
         <v>360</v>
       </c>
       <c r="OW9" s="98">
@@ -33507,7 +34114,7 @@
         <v>1.44</v>
       </c>
       <c r="PD9" s="48">
-        <f t="shared" ref="PD9:PD10" si="199">PB9*PC9</f>
+        <f t="shared" ref="PD9:PD10" si="202">PB9*PC9</f>
         <v>360</v>
       </c>
       <c r="PE9" s="98">
@@ -33563,7 +34170,7 @@
         <v>1.44</v>
       </c>
       <c r="PT9" s="48">
-        <f t="shared" ref="PT9:PT10" si="200">PR9*PS9</f>
+        <f t="shared" ref="PT9:PT10" si="203">PR9*PS9</f>
         <v>360</v>
       </c>
       <c r="PU9" s="98">
@@ -33595,7 +34202,7 @@
         <v>1.44</v>
       </c>
       <c r="QC9" s="48">
-        <f t="shared" ref="QC9:QC10" si="201">QA9*QB9</f>
+        <f t="shared" ref="QC9:QC10" si="204">QA9*QB9</f>
         <v>360</v>
       </c>
       <c r="QD9" s="98">
@@ -33622,7 +34229,7 @@
         <v>1.44</v>
       </c>
       <c r="QK9" s="48">
-        <f t="shared" ref="QK9:QK10" si="202">QI9*QJ9</f>
+        <f t="shared" ref="QK9:QK10" si="205">QI9*QJ9</f>
         <v>360</v>
       </c>
       <c r="QL9" s="98">
@@ -33649,7 +34256,7 @@
         <v>1.44</v>
       </c>
       <c r="QT9" s="48">
-        <f t="shared" ref="QT9:QT10" si="203">QR9*QS9</f>
+        <f t="shared" ref="QT9:QT10" si="206">QR9*QS9</f>
         <v>360</v>
       </c>
       <c r="QU9" s="98">
@@ -33676,7 +34283,7 @@
         <v>1.44</v>
       </c>
       <c r="RB9" s="48">
-        <f t="shared" ref="RB9:RB10" si="204">QZ9*RA9</f>
+        <f t="shared" ref="RB9:RB10" si="207">QZ9*RA9</f>
         <v>360</v>
       </c>
       <c r="RC9" s="98">
@@ -33703,7 +34310,7 @@
         <v>1.44</v>
       </c>
       <c r="RK9" s="48">
-        <f t="shared" ref="RK9:RK10" si="205">RI9*RJ9</f>
+        <f t="shared" ref="RK9:RK10" si="208">RI9*RJ9</f>
         <v>360</v>
       </c>
       <c r="RL9" s="98">
@@ -33730,7 +34337,7 @@
         <v>1.44</v>
       </c>
       <c r="RT9" s="48">
-        <f t="shared" ref="RT9:RT10" si="206">RR9*RS9</f>
+        <f t="shared" ref="RT9:RT10" si="209">RR9*RS9</f>
         <v>360</v>
       </c>
       <c r="RU9" s="98"/>
@@ -33755,7 +34362,7 @@
         <v>1.44</v>
       </c>
       <c r="SC9" s="48">
-        <f t="shared" ref="SC9:SC10" si="207">SA9*SB9</f>
+        <f t="shared" ref="SC9:SC10" si="210">SA9*SB9</f>
         <v>360</v>
       </c>
       <c r="SD9" s="98"/>
@@ -33780,7 +34387,7 @@
         <v>1.44</v>
       </c>
       <c r="SL9" s="48">
-        <f t="shared" ref="SL9:SL10" si="208">SJ9*SK9</f>
+        <f t="shared" ref="SL9:SL10" si="211">SJ9*SK9</f>
         <v>360</v>
       </c>
       <c r="SM9" s="98"/>
@@ -33805,7 +34412,7 @@
         <v>1.44</v>
       </c>
       <c r="SU9" s="48">
-        <f t="shared" ref="SU9:SU10" si="209">SS9*ST9</f>
+        <f t="shared" ref="SU9:SU10" si="212">SS9*ST9</f>
         <v>360</v>
       </c>
       <c r="SV9" s="98"/>
@@ -33830,7 +34437,7 @@
         <v>1.44</v>
       </c>
       <c r="TD9" s="48">
-        <f t="shared" ref="TD9:TD10" si="210">TB9*TC9</f>
+        <f t="shared" ref="TD9:TD10" si="213">TB9*TC9</f>
         <v>360</v>
       </c>
       <c r="TE9" s="98"/>
@@ -33855,7 +34462,7 @@
         <v>1.44</v>
       </c>
       <c r="TM9" s="48">
-        <f t="shared" ref="TM9:TM10" si="211">TK9*TL9</f>
+        <f t="shared" ref="TM9:TM10" si="214">TK9*TL9</f>
         <v>360</v>
       </c>
       <c r="TN9" s="98"/>
@@ -33880,7 +34487,7 @@
         <v>1.44</v>
       </c>
       <c r="TV9" s="48">
-        <f t="shared" ref="TV9:TV10" si="212">TT9*TU9</f>
+        <f t="shared" ref="TV9:TV10" si="215">TT9*TU9</f>
         <v>360</v>
       </c>
       <c r="TW9" s="98"/>
@@ -33905,7 +34512,7 @@
         <v>1.44</v>
       </c>
       <c r="UE9" s="48">
-        <f t="shared" ref="UE9:UE10" si="213">UC9*UD9</f>
+        <f t="shared" ref="UE9:UE10" si="216">UC9*UD9</f>
         <v>360</v>
       </c>
       <c r="UF9" s="98"/>
@@ -33930,7 +34537,7 @@
         <v>1.44</v>
       </c>
       <c r="UN9" s="48">
-        <f t="shared" ref="UN9:UN10" si="214">UL9*UM9</f>
+        <f t="shared" ref="UN9:UN10" si="217">UL9*UM9</f>
         <v>360</v>
       </c>
       <c r="UO9" s="98"/>
@@ -33955,7 +34562,7 @@
         <v>1.44</v>
       </c>
       <c r="UW9" s="48">
-        <f t="shared" ref="UW9:UW10" si="215">UU9*UV9</f>
+        <f t="shared" ref="UW9:UW10" si="218">UU9*UV9</f>
         <v>360</v>
       </c>
       <c r="UX9" s="98"/>
@@ -33980,7 +34587,7 @@
         <v>1.44</v>
       </c>
       <c r="VF9" s="48">
-        <f t="shared" ref="VF9:VF10" si="216">VD9*VE9</f>
+        <f t="shared" ref="VF9:VF10" si="219">VD9*VE9</f>
         <v>360</v>
       </c>
       <c r="VG9" s="98"/>
@@ -34005,7 +34612,7 @@
         <v>1.44</v>
       </c>
       <c r="VO9" s="48">
-        <f t="shared" ref="VO9:VO10" si="217">VM9*VN9</f>
+        <f t="shared" ref="VO9:VO10" si="220">VM9*VN9</f>
         <v>360</v>
       </c>
       <c r="VP9" s="98"/>
@@ -34030,7 +34637,7 @@
         <v>1.44</v>
       </c>
       <c r="VX9" s="48">
-        <f t="shared" ref="VX9:VX10" si="218">VV9*VW9</f>
+        <f t="shared" ref="VX9:VX10" si="221">VV9*VW9</f>
         <v>360</v>
       </c>
       <c r="VY9" s="98"/>
@@ -34055,7 +34662,7 @@
         <v>1.44</v>
       </c>
       <c r="WG9" s="48">
-        <f t="shared" ref="WG9:WG10" si="219">WE9*WF9</f>
+        <f t="shared" ref="WG9:WG10" si="222">WE9*WF9</f>
         <v>360</v>
       </c>
       <c r="WH9" s="98"/>
@@ -34080,7 +34687,7 @@
         <v>1.44</v>
       </c>
       <c r="WP9" s="48">
-        <f t="shared" ref="WP9:WP10" si="220">WN9*WO9</f>
+        <f t="shared" ref="WP9:WP10" si="223">WN9*WO9</f>
         <v>360</v>
       </c>
       <c r="WQ9" s="98"/>
@@ -34105,7 +34712,7 @@
         <v>1.44</v>
       </c>
       <c r="WY9" s="48">
-        <f t="shared" ref="WY9:WY10" si="221">WW9*WX9</f>
+        <f t="shared" ref="WY9:WY10" si="224">WW9*WX9</f>
         <v>360</v>
       </c>
       <c r="WZ9" s="98"/>
@@ -34130,7 +34737,7 @@
         <v>1.44</v>
       </c>
       <c r="XH9" s="48">
-        <f t="shared" ref="XH9:XH10" si="222">XF9*XG9</f>
+        <f t="shared" ref="XH9:XH10" si="225">XF9*XG9</f>
         <v>360</v>
       </c>
       <c r="XI9" s="98"/>
@@ -34155,7 +34762,7 @@
         <v>1.44</v>
       </c>
       <c r="XQ9" s="48">
-        <f t="shared" ref="XQ9:XQ10" si="223">XO9*XP9</f>
+        <f t="shared" ref="XQ9:XQ10" si="226">XO9*XP9</f>
         <v>360</v>
       </c>
       <c r="XR9" s="98"/>
@@ -34180,7 +34787,7 @@
         <v>1.44</v>
       </c>
       <c r="XZ9" s="48">
-        <f t="shared" ref="XZ9:XZ10" si="224">XX9*XY9</f>
+        <f t="shared" ref="XZ9:XZ10" si="227">XX9*XY9</f>
         <v>360</v>
       </c>
       <c r="YA9" s="98"/>
@@ -34205,7 +34812,7 @@
         <v>1.44</v>
       </c>
       <c r="YI9" s="48">
-        <f t="shared" ref="YI9:YI10" si="225">YG9*YH9</f>
+        <f t="shared" ref="YI9:YI10" si="228">YG9*YH9</f>
         <v>360</v>
       </c>
       <c r="YJ9" s="98"/>
@@ -34230,7 +34837,7 @@
         <v>1.44</v>
       </c>
       <c r="YR9" s="48">
-        <f t="shared" ref="YR9:YR10" si="226">YP9*YQ9</f>
+        <f t="shared" ref="YR9:YR10" si="229">YP9*YQ9</f>
         <v>360</v>
       </c>
       <c r="YS9" s="98"/>
@@ -34255,7 +34862,7 @@
         <v>1.44</v>
       </c>
       <c r="ZA9" s="48">
-        <f t="shared" ref="ZA9:ZA10" si="227">YY9*YZ9</f>
+        <f t="shared" ref="ZA9:ZA10" si="230">YY9*YZ9</f>
         <v>360</v>
       </c>
       <c r="ZB9" s="98"/>
@@ -34267,8 +34874,33 @@
         <f>ZA11</f>
         <v>1874.4</v>
       </c>
-    </row>
-    <row r="10" spans="2:680" x14ac:dyDescent="0.25">
+      <c r="ZF9" s="280">
+        <v>53510</v>
+      </c>
+      <c r="ZG9" s="280">
+        <v>53400</v>
+      </c>
+      <c r="ZH9" s="46">
+        <v>250</v>
+      </c>
+      <c r="ZI9" s="48">
+        <v>1.44</v>
+      </c>
+      <c r="ZJ9" s="48">
+        <f t="shared" ref="ZJ9:ZJ10" si="231">ZH9*ZI9</f>
+        <v>360</v>
+      </c>
+      <c r="ZK9" s="98"/>
+      <c r="ZL9" s="306">
+        <f>ZJ11</f>
+        <v>290.40000000000003</v>
+      </c>
+      <c r="ZM9" s="321">
+        <f>ZJ11</f>
+        <v>290.40000000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="2:689" x14ac:dyDescent="0.25">
       <c r="B10" s="46"/>
       <c r="C10" s="47"/>
       <c r="D10" s="228"/>
@@ -34362,7 +34994,7 @@
       <c r="AX10" s="49"/>
       <c r="AY10" s="99"/>
       <c r="AZ10" s="99">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="BA10" s="67"/>
@@ -34380,7 +35012,7 @@
       <c r="BF10" s="49"/>
       <c r="BG10" s="99"/>
       <c r="BH10" s="99">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="BI10" s="67"/>
@@ -34398,7 +35030,7 @@
       <c r="BN10" s="49"/>
       <c r="BO10" s="99"/>
       <c r="BP10" s="99">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0</v>
       </c>
       <c r="BQ10" s="67"/>
@@ -34416,7 +35048,7 @@
       <c r="BV10" s="49"/>
       <c r="BW10" s="99"/>
       <c r="BX10" s="99">
-        <f t="shared" ref="BX10:BX17" si="228">BW10</f>
+        <f t="shared" ref="BX10:BX17" si="232">BW10</f>
         <v>0</v>
       </c>
       <c r="BY10" s="67"/>
@@ -34434,7 +35066,7 @@
       <c r="CD10" s="49"/>
       <c r="CE10" s="99"/>
       <c r="CF10" s="99">
-        <f t="shared" ref="CF10:CF11" si="229">CE10</f>
+        <f t="shared" ref="CF10:CF11" si="233">CE10</f>
         <v>0</v>
       </c>
       <c r="CI10" s="67"/>
@@ -34452,7 +35084,7 @@
       <c r="CN10" s="49"/>
       <c r="CO10" s="99"/>
       <c r="CP10" s="99">
-        <f t="shared" ref="CP10:CP11" si="230">CO10</f>
+        <f t="shared" ref="CP10:CP11" si="234">CO10</f>
         <v>0</v>
       </c>
       <c r="CQ10" s="67"/>
@@ -34470,7 +35102,7 @@
       <c r="CV10" s="49"/>
       <c r="CW10" s="99"/>
       <c r="CX10" s="99">
-        <f t="shared" ref="CX10:CX11" si="231">CW10</f>
+        <f t="shared" ref="CX10:CX11" si="235">CW10</f>
         <v>0</v>
       </c>
       <c r="CY10" s="67"/>
@@ -34488,7 +35120,7 @@
       <c r="DD10" s="49"/>
       <c r="DE10" s="99"/>
       <c r="DF10" s="142">
-        <f t="shared" ref="DF10:DF11" si="232">DE10</f>
+        <f t="shared" ref="DF10:DF11" si="236">DE10</f>
         <v>0</v>
       </c>
       <c r="DG10" s="67"/>
@@ -34506,7 +35138,7 @@
       <c r="DL10" s="49"/>
       <c r="DM10" s="128"/>
       <c r="DN10" s="140">
-        <f t="shared" ref="DN10:DN11" si="233">DM10</f>
+        <f t="shared" ref="DN10:DN11" si="237">DM10</f>
         <v>0</v>
       </c>
       <c r="DO10" s="67"/>
@@ -34524,7 +35156,7 @@
       <c r="DT10" s="49"/>
       <c r="DU10" s="128"/>
       <c r="DV10" s="140">
-        <f t="shared" ref="DV10:DV11" si="234">DU10</f>
+        <f t="shared" ref="DV10:DV11" si="238">DU10</f>
         <v>0</v>
       </c>
       <c r="DW10" s="67"/>
@@ -34542,7 +35174,7 @@
       <c r="EB10" s="49"/>
       <c r="EC10" s="128"/>
       <c r="ED10" s="140">
-        <f t="shared" ref="ED10:ED11" si="235">EC10</f>
+        <f t="shared" ref="ED10:ED11" si="239">EC10</f>
         <v>0</v>
       </c>
       <c r="EE10" s="67"/>
@@ -34560,7 +35192,7 @@
       <c r="EJ10" s="49"/>
       <c r="EK10" s="128"/>
       <c r="EL10" s="140">
-        <f t="shared" ref="EL10:EL11" si="236">EK10</f>
+        <f t="shared" ref="EL10:EL11" si="240">EK10</f>
         <v>0</v>
       </c>
       <c r="EM10" s="67"/>
@@ -34578,7 +35210,7 @@
       <c r="ER10" s="49"/>
       <c r="ES10" s="128"/>
       <c r="ET10" s="140">
-        <f t="shared" ref="ET10:ET11" si="237">ES10</f>
+        <f t="shared" ref="ET10:ET11" si="241">ES10</f>
         <v>0</v>
       </c>
       <c r="EU10" s="67"/>
@@ -34596,7 +35228,7 @@
       <c r="EZ10" s="49"/>
       <c r="FA10" s="128"/>
       <c r="FB10" s="140">
-        <f t="shared" ref="FB10:FB11" si="238">FA10</f>
+        <f t="shared" ref="FB10:FB11" si="242">FA10</f>
         <v>0</v>
       </c>
       <c r="FC10" s="67"/>
@@ -34614,7 +35246,7 @@
       <c r="FH10" s="49"/>
       <c r="FI10" s="128"/>
       <c r="FJ10" s="140">
-        <f t="shared" ref="FJ10:FJ11" si="239">FI10</f>
+        <f t="shared" ref="FJ10:FJ11" si="243">FI10</f>
         <v>0</v>
       </c>
       <c r="FK10" s="67"/>
@@ -34632,7 +35264,7 @@
       <c r="FP10" s="49"/>
       <c r="FQ10" s="128"/>
       <c r="FR10" s="182">
-        <f t="shared" ref="FR10:FR11" si="240">FQ10</f>
+        <f t="shared" ref="FR10:FR11" si="244">FQ10</f>
         <v>0</v>
       </c>
       <c r="FS10" s="67"/>
@@ -34650,7 +35282,7 @@
       <c r="FX10" s="49"/>
       <c r="FY10" s="128"/>
       <c r="FZ10" s="182">
-        <f t="shared" ref="FZ10:FZ11" si="241">FY10</f>
+        <f t="shared" ref="FZ10:FZ11" si="245">FY10</f>
         <v>0</v>
       </c>
       <c r="GA10" s="67"/>
@@ -34662,13 +35294,13 @@
         <v>1.68</v>
       </c>
       <c r="GE10" s="48">
-        <f t="shared" si="170"/>
+        <f t="shared" si="173"/>
         <v>549.36</v>
       </c>
       <c r="GF10" s="49"/>
       <c r="GG10" s="128"/>
       <c r="GH10" s="182">
-        <f t="shared" ref="GH10:GH11" si="242">GG10</f>
+        <f t="shared" ref="GH10:GH11" si="246">GG10</f>
         <v>0</v>
       </c>
       <c r="GI10" s="67"/>
@@ -34680,13 +35312,13 @@
         <v>1.68</v>
       </c>
       <c r="GM10" s="48">
-        <f t="shared" si="171"/>
+        <f t="shared" si="174"/>
         <v>366.24</v>
       </c>
       <c r="GN10" s="49"/>
       <c r="GO10" s="128"/>
       <c r="GP10" s="182">
-        <f t="shared" ref="GP10:GP11" si="243">GO10</f>
+        <f t="shared" ref="GP10:GP11" si="247">GO10</f>
         <v>0</v>
       </c>
       <c r="GQ10" s="67"/>
@@ -34698,13 +35330,13 @@
         <v>1.68</v>
       </c>
       <c r="GU10" s="48">
-        <f t="shared" si="172"/>
+        <f t="shared" si="175"/>
         <v>349.44</v>
       </c>
       <c r="GV10" s="49"/>
       <c r="GW10" s="128"/>
       <c r="GX10" s="182">
-        <f t="shared" ref="GX10:GX11" si="244">GW10</f>
+        <f t="shared" ref="GX10:GX11" si="248">GW10</f>
         <v>0</v>
       </c>
       <c r="GY10" s="67"/>
@@ -34716,13 +35348,13 @@
         <v>1.68</v>
       </c>
       <c r="HC10" s="48">
-        <f t="shared" si="173"/>
+        <f t="shared" si="176"/>
         <v>349.44</v>
       </c>
       <c r="HD10" s="49"/>
       <c r="HE10" s="128"/>
       <c r="HF10" s="182">
-        <f t="shared" ref="HF10:HF11" si="245">HE10</f>
+        <f t="shared" ref="HF10:HF11" si="249">HE10</f>
         <v>0</v>
       </c>
       <c r="HG10" s="67"/>
@@ -34734,13 +35366,13 @@
         <v>1.68</v>
       </c>
       <c r="HK10" s="48">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>428.4</v>
       </c>
       <c r="HL10" s="49"/>
       <c r="HM10" s="128"/>
       <c r="HN10" s="182">
-        <f t="shared" ref="HN10:HN11" si="246">HM10</f>
+        <f t="shared" ref="HN10:HN11" si="250">HM10</f>
         <v>0</v>
       </c>
       <c r="HO10" s="67"/>
@@ -34752,13 +35384,13 @@
         <v>1.68</v>
       </c>
       <c r="HS10" s="48">
-        <f t="shared" si="175"/>
+        <f t="shared" si="178"/>
         <v>643.43999999999994</v>
       </c>
       <c r="HT10" s="49"/>
       <c r="HU10" s="128"/>
       <c r="HV10" s="182">
-        <f t="shared" ref="HV10:HV11" si="247">HU10</f>
+        <f t="shared" ref="HV10:HV11" si="251">HU10</f>
         <v>0</v>
       </c>
       <c r="HW10" s="67"/>
@@ -34770,13 +35402,13 @@
         <v>1.68</v>
       </c>
       <c r="IA10" s="48">
-        <f t="shared" si="176"/>
+        <f t="shared" si="179"/>
         <v>742.56</v>
       </c>
       <c r="IB10" s="49"/>
       <c r="IC10" s="128"/>
       <c r="ID10" s="182">
-        <f t="shared" ref="ID10:ID11" si="248">IC10</f>
+        <f t="shared" ref="ID10:ID11" si="252">IC10</f>
         <v>0</v>
       </c>
       <c r="IE10" s="67"/>
@@ -34788,13 +35420,13 @@
         <v>1.68</v>
       </c>
       <c r="II10" s="48">
-        <f t="shared" si="177"/>
+        <f t="shared" si="180"/>
         <v>841.68</v>
       </c>
       <c r="IJ10" s="49"/>
       <c r="IK10" s="128"/>
       <c r="IL10" s="182">
-        <f t="shared" ref="IL10:IL11" si="249">IK10</f>
+        <f t="shared" ref="IL10:IL11" si="253">IK10</f>
         <v>0</v>
       </c>
       <c r="IM10" s="67"/>
@@ -34806,13 +35438,13 @@
         <v>1.68</v>
       </c>
       <c r="IQ10" s="48">
-        <f t="shared" si="178"/>
+        <f t="shared" si="181"/>
         <v>804.71999999999991</v>
       </c>
       <c r="IR10" s="49"/>
       <c r="IS10" s="128"/>
       <c r="IT10" s="182">
-        <f t="shared" ref="IT10:IT11" si="250">IS10</f>
+        <f t="shared" ref="IT10:IT11" si="254">IS10</f>
         <v>0</v>
       </c>
       <c r="IU10" s="67"/>
@@ -34824,13 +35456,13 @@
         <v>1.68</v>
       </c>
       <c r="IY10" s="48">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>880.31999999999994</v>
       </c>
       <c r="IZ10" s="49"/>
       <c r="JA10" s="128"/>
       <c r="JB10" s="182">
-        <f t="shared" ref="JB10:JB11" si="251">JA10</f>
+        <f t="shared" ref="JB10:JB11" si="255">JA10</f>
         <v>0</v>
       </c>
       <c r="JC10" s="67"/>
@@ -34842,13 +35474,13 @@
         <v>1.68</v>
       </c>
       <c r="JG10" s="48">
-        <f t="shared" si="180"/>
+        <f t="shared" si="183"/>
         <v>994.56</v>
       </c>
       <c r="JH10" s="49"/>
       <c r="JI10" s="128"/>
       <c r="JJ10" s="231">
-        <f t="shared" ref="JJ10:JJ11" si="252">JI10</f>
+        <f t="shared" ref="JJ10:JJ11" si="256">JI10</f>
         <v>0</v>
       </c>
       <c r="JK10" s="67"/>
@@ -34860,13 +35492,13 @@
         <v>1.68</v>
       </c>
       <c r="JO10" s="48">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>981.12</v>
       </c>
       <c r="JP10" s="49"/>
       <c r="JQ10" s="128"/>
       <c r="JR10" s="231">
-        <f t="shared" ref="JR10:JR11" si="253">JQ10</f>
+        <f t="shared" ref="JR10:JR11" si="257">JQ10</f>
         <v>0</v>
       </c>
       <c r="JS10" s="67"/>
@@ -34878,13 +35510,13 @@
         <v>1.68</v>
       </c>
       <c r="JW10" s="48">
-        <f t="shared" si="182"/>
+        <f t="shared" si="185"/>
         <v>420</v>
       </c>
       <c r="JX10" s="49"/>
       <c r="JY10" s="128"/>
       <c r="JZ10" s="231">
-        <f t="shared" ref="JZ10:JZ11" si="254">JY10</f>
+        <f t="shared" ref="JZ10:JZ11" si="258">JY10</f>
         <v>0</v>
       </c>
       <c r="KA10" s="67"/>
@@ -34896,13 +35528,13 @@
         <v>1.68</v>
       </c>
       <c r="KE10" s="48">
-        <f t="shared" si="183"/>
+        <f t="shared" si="186"/>
         <v>431.76</v>
       </c>
       <c r="KF10" s="49"/>
       <c r="KG10" s="128"/>
       <c r="KH10" s="231">
-        <f t="shared" ref="KH10:KH11" si="255">KG10</f>
+        <f t="shared" ref="KH10:KH11" si="259">KG10</f>
         <v>0</v>
       </c>
       <c r="KI10" s="67"/>
@@ -34914,13 +35546,13 @@
         <v>1.68</v>
       </c>
       <c r="KM10" s="48">
-        <f t="shared" si="184"/>
+        <f t="shared" si="187"/>
         <v>431.76</v>
       </c>
       <c r="KN10" s="49"/>
       <c r="KO10" s="128"/>
       <c r="KP10" s="231">
-        <f t="shared" ref="KP10:KP11" si="256">KO10</f>
+        <f t="shared" ref="KP10:KP11" si="260">KO10</f>
         <v>0</v>
       </c>
       <c r="KQ10" s="67"/>
@@ -34932,13 +35564,13 @@
         <v>1.68</v>
       </c>
       <c r="KU10" s="48">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>341.03999999999996</v>
       </c>
       <c r="KV10" s="49"/>
       <c r="KW10" s="128"/>
       <c r="KX10" s="231">
-        <f t="shared" ref="KX10:KX11" si="257">KW10</f>
+        <f t="shared" ref="KX10:KX11" si="261">KW10</f>
         <v>0</v>
       </c>
       <c r="KY10" s="67"/>
@@ -34950,13 +35582,13 @@
         <v>1.68</v>
       </c>
       <c r="LC10" s="48">
-        <f t="shared" si="186"/>
+        <f t="shared" si="189"/>
         <v>431.76</v>
       </c>
       <c r="LD10" s="49"/>
       <c r="LE10" s="128"/>
       <c r="LF10" s="231">
-        <f t="shared" ref="LF10:LF11" si="258">LE10</f>
+        <f t="shared" ref="LF10:LF11" si="262">LE10</f>
         <v>0</v>
       </c>
       <c r="LG10" s="67"/>
@@ -34974,7 +35606,7 @@
       <c r="LL10" s="49"/>
       <c r="LM10" s="128"/>
       <c r="LN10" s="231">
-        <f t="shared" ref="LN10:LN11" si="259">LM10</f>
+        <f t="shared" ref="LN10:LN11" si="263">LM10</f>
         <v>0</v>
       </c>
       <c r="LO10" s="67"/>
@@ -34992,7 +35624,7 @@
       <c r="LT10" s="49"/>
       <c r="LU10" s="128"/>
       <c r="LV10" s="231">
-        <f t="shared" ref="LV10:LV11" si="260">LU10</f>
+        <f t="shared" ref="LV10:LV11" si="264">LU10</f>
         <v>0</v>
       </c>
       <c r="LW10" s="278"/>
@@ -35010,7 +35642,7 @@
       <c r="MB10" s="49"/>
       <c r="MC10" s="231"/>
       <c r="MD10" s="250">
-        <f t="shared" ref="MD10:MD11" si="261">MC10</f>
+        <f t="shared" ref="MD10:MD11" si="265">MC10</f>
         <v>0</v>
       </c>
       <c r="MF10" s="278"/>
@@ -35021,7 +35653,7 @@
       <c r="MK10" s="49"/>
       <c r="ML10" s="231"/>
       <c r="MM10" s="250">
-        <f t="shared" ref="MM10:MM11" si="262">ML10</f>
+        <f t="shared" ref="MM10:MM11" si="266">ML10</f>
         <v>0</v>
       </c>
       <c r="MN10" s="278"/>
@@ -35032,7 +35664,7 @@
       <c r="MS10" s="49"/>
       <c r="MT10" s="231"/>
       <c r="MU10" s="250">
-        <f t="shared" ref="MU10:MU11" si="263">MT10</f>
+        <f t="shared" ref="MU10:MU11" si="267">MT10</f>
         <v>0</v>
       </c>
       <c r="MV10" s="278"/>
@@ -35043,7 +35675,7 @@
       <c r="NA10" s="49"/>
       <c r="NB10" s="231"/>
       <c r="NC10" s="250">
-        <f t="shared" ref="NC10:NC11" si="264">NB10</f>
+        <f t="shared" ref="NC10:NC11" si="268">NB10</f>
         <v>0</v>
       </c>
       <c r="ND10" s="278"/>
@@ -35054,7 +35686,7 @@
       <c r="NI10" s="49"/>
       <c r="NJ10" s="231"/>
       <c r="NK10" s="250">
-        <f t="shared" ref="NK10:NK11" si="265">NJ10</f>
+        <f t="shared" ref="NK10:NK11" si="269">NJ10</f>
         <v>0</v>
       </c>
       <c r="NL10" s="278"/>
@@ -35065,7 +35697,7 @@
       <c r="NQ10" s="49"/>
       <c r="NR10" s="231"/>
       <c r="NS10" s="250">
-        <f t="shared" ref="NS10:NS11" si="266">NR10</f>
+        <f t="shared" ref="NS10:NS11" si="270">NR10</f>
         <v>0</v>
       </c>
       <c r="NT10" s="278"/>
@@ -35076,7 +35708,7 @@
       <c r="NY10" s="49"/>
       <c r="NZ10" s="231"/>
       <c r="OA10" s="250">
-        <f t="shared" ref="OA10:OA11" si="267">NZ10</f>
+        <f t="shared" ref="OA10:OA11" si="271">NZ10</f>
         <v>0</v>
       </c>
       <c r="OB10" s="278"/>
@@ -35087,7 +35719,7 @@
       <c r="OG10" s="49"/>
       <c r="OH10" s="231"/>
       <c r="OI10" s="250">
-        <f t="shared" ref="OI10:OI11" si="268">OH10</f>
+        <f t="shared" ref="OI10:OI11" si="272">OH10</f>
         <v>0</v>
       </c>
       <c r="OJ10" s="278"/>
@@ -35098,7 +35730,7 @@
       <c r="OO10" s="49"/>
       <c r="OP10" s="231"/>
       <c r="OQ10" s="250">
-        <f t="shared" ref="OQ10:OQ11" si="269">OP10</f>
+        <f t="shared" ref="OQ10:OQ11" si="273">OP10</f>
         <v>0</v>
       </c>
       <c r="OR10" s="278"/>
@@ -35110,13 +35742,13 @@
         <v>1.68</v>
       </c>
       <c r="OV10" s="48">
-        <f t="shared" ref="OV10" si="270">OT10*OU10</f>
+        <f t="shared" ref="OV10" si="274">OT10*OU10</f>
         <v>504</v>
       </c>
       <c r="OW10" s="49"/>
       <c r="OX10" s="231"/>
       <c r="OY10" s="250">
-        <f t="shared" ref="OY10:OY11" si="271">OX10</f>
+        <f t="shared" ref="OY10:OY11" si="275">OX10</f>
         <v>0</v>
       </c>
       <c r="OZ10" s="278"/>
@@ -35129,13 +35761,13 @@
         <v>1.68</v>
       </c>
       <c r="PD10" s="48">
-        <f t="shared" si="199"/>
+        <f t="shared" si="202"/>
         <v>369.59999999999997</v>
       </c>
       <c r="PE10" s="49"/>
       <c r="PF10" s="231"/>
       <c r="PG10" s="250">
-        <f t="shared" ref="PG10:PG11" si="272">PF10</f>
+        <f t="shared" ref="PG10:PG11" si="276">PF10</f>
         <v>0</v>
       </c>
       <c r="PH10" s="278"/>
@@ -35148,13 +35780,13 @@
         <v>1.68</v>
       </c>
       <c r="PL10" s="48">
-        <f t="shared" ref="PL10" si="273">PJ10*PK10</f>
+        <f t="shared" ref="PL10" si="277">PJ10*PK10</f>
         <v>443.52</v>
       </c>
       <c r="PM10" s="49"/>
       <c r="PN10" s="231"/>
       <c r="PO10" s="250">
-        <f t="shared" ref="PO10:PO11" si="274">PN10</f>
+        <f t="shared" ref="PO10:PO11" si="278">PN10</f>
         <v>0</v>
       </c>
       <c r="PP10" s="278"/>
@@ -35167,13 +35799,13 @@
         <v>1.68</v>
       </c>
       <c r="PT10" s="48">
-        <f t="shared" si="200"/>
+        <f t="shared" si="203"/>
         <v>530.88</v>
       </c>
       <c r="PU10" s="49"/>
       <c r="PV10" s="231"/>
       <c r="PW10" s="250">
-        <f t="shared" ref="PW10:PW11" si="275">PV10</f>
+        <f t="shared" ref="PW10:PW11" si="279">PV10</f>
         <v>0</v>
       </c>
       <c r="PY10" s="278"/>
@@ -35186,7 +35818,7 @@
         <v>1.68</v>
       </c>
       <c r="QC10" s="48">
-        <f t="shared" si="201"/>
+        <f t="shared" si="204"/>
         <v>401.52</v>
       </c>
       <c r="QD10" s="49"/>
@@ -35202,7 +35834,7 @@
         <v>1.68</v>
       </c>
       <c r="QK10" s="48">
-        <f t="shared" si="202"/>
+        <f t="shared" si="205"/>
         <v>367.91999999999996</v>
       </c>
       <c r="QL10" s="49"/>
@@ -35218,7 +35850,7 @@
         <v>1.68</v>
       </c>
       <c r="QT10" s="48">
-        <f t="shared" si="203"/>
+        <f t="shared" si="206"/>
         <v>388.08</v>
       </c>
       <c r="QU10" s="49"/>
@@ -35234,7 +35866,7 @@
         <v>1.68</v>
       </c>
       <c r="RB10" s="48">
-        <f t="shared" si="204"/>
+        <f t="shared" si="207"/>
         <v>299.03999999999996</v>
       </c>
       <c r="RC10" s="49"/>
@@ -35250,7 +35882,7 @@
         <v>1.68</v>
       </c>
       <c r="RK10" s="48">
-        <f t="shared" si="205"/>
+        <f t="shared" si="208"/>
         <v>248.64</v>
       </c>
       <c r="RL10" s="49"/>
@@ -35266,7 +35898,7 @@
         <v>1.68</v>
       </c>
       <c r="RT10" s="48">
-        <f t="shared" si="206"/>
+        <f t="shared" si="209"/>
         <v>304.08</v>
       </c>
       <c r="RU10" s="49"/>
@@ -35282,7 +35914,7 @@
         <v>1.68</v>
       </c>
       <c r="SC10" s="48">
-        <f t="shared" si="207"/>
+        <f t="shared" si="210"/>
         <v>527.52</v>
       </c>
       <c r="SD10" s="49"/>
@@ -35298,7 +35930,7 @@
         <v>1.68</v>
       </c>
       <c r="SL10" s="48">
-        <f t="shared" si="208"/>
+        <f t="shared" si="211"/>
         <v>223.44</v>
       </c>
       <c r="SM10" s="49"/>
@@ -35314,7 +35946,7 @@
         <v>1.68</v>
       </c>
       <c r="SU10" s="48">
-        <f t="shared" si="209"/>
+        <f t="shared" si="212"/>
         <v>414.96</v>
       </c>
       <c r="SV10" s="49"/>
@@ -35330,7 +35962,7 @@
         <v>1.68</v>
       </c>
       <c r="TD10" s="48">
-        <f t="shared" si="210"/>
+        <f t="shared" si="213"/>
         <v>487.2</v>
       </c>
       <c r="TE10" s="49"/>
@@ -35346,7 +35978,7 @@
         <v>1.68</v>
       </c>
       <c r="TM10" s="48">
-        <f t="shared" si="211"/>
+        <f t="shared" si="214"/>
         <v>551.04</v>
       </c>
       <c r="TN10" s="49"/>
@@ -35362,7 +35994,7 @@
         <v>1.68</v>
       </c>
       <c r="TV10" s="48">
-        <f t="shared" si="212"/>
+        <f t="shared" si="215"/>
         <v>220.07999999999998</v>
       </c>
       <c r="TW10" s="49"/>
@@ -35378,7 +36010,7 @@
         <v>1.68</v>
       </c>
       <c r="UE10" s="48">
-        <f t="shared" si="213"/>
+        <f t="shared" si="216"/>
         <v>530.88</v>
       </c>
       <c r="UF10" s="49"/>
@@ -35394,7 +36026,7 @@
         <v>1.68</v>
       </c>
       <c r="UN10" s="48">
-        <f t="shared" si="214"/>
+        <f t="shared" si="217"/>
         <v>483.84</v>
       </c>
       <c r="UO10" s="49"/>
@@ -35410,7 +36042,7 @@
         <v>1.68</v>
       </c>
       <c r="UW10" s="48">
-        <f t="shared" si="215"/>
+        <f t="shared" si="218"/>
         <v>349.44</v>
       </c>
       <c r="UX10" s="49"/>
@@ -35426,7 +36058,7 @@
         <v>1.68</v>
       </c>
       <c r="VF10" s="48">
-        <f t="shared" si="216"/>
+        <f t="shared" si="219"/>
         <v>354.47999999999996</v>
       </c>
       <c r="VG10" s="49"/>
@@ -35442,7 +36074,7 @@
         <v>1.68</v>
       </c>
       <c r="VO10" s="48">
-        <f t="shared" si="217"/>
+        <f t="shared" si="220"/>
         <v>231.84</v>
       </c>
       <c r="VP10" s="49"/>
@@ -35458,7 +36090,7 @@
         <v>1.68</v>
       </c>
       <c r="VX10" s="48">
-        <f t="shared" si="218"/>
+        <f t="shared" si="221"/>
         <v>252</v>
       </c>
       <c r="VY10" s="49"/>
@@ -35474,7 +36106,7 @@
         <v>1.68</v>
       </c>
       <c r="WG10" s="48">
-        <f t="shared" si="219"/>
+        <f t="shared" si="222"/>
         <v>310.8</v>
       </c>
       <c r="WH10" s="49"/>
@@ -35490,7 +36122,7 @@
         <v>1.68</v>
       </c>
       <c r="WP10" s="48">
-        <f t="shared" si="220"/>
+        <f t="shared" si="223"/>
         <v>228.48</v>
       </c>
       <c r="WQ10" s="49"/>
@@ -35506,7 +36138,7 @@
         <v>1.68</v>
       </c>
       <c r="WY10" s="48">
-        <f t="shared" si="221"/>
+        <f t="shared" si="224"/>
         <v>406.56</v>
       </c>
       <c r="WZ10" s="49"/>
@@ -35522,7 +36154,7 @@
         <v>1.68</v>
       </c>
       <c r="XH10" s="48">
-        <f t="shared" si="222"/>
+        <f t="shared" si="225"/>
         <v>342.71999999999997</v>
       </c>
       <c r="XI10" s="49"/>
@@ -35538,7 +36170,7 @@
         <v>1.68</v>
       </c>
       <c r="XQ10" s="48">
-        <f t="shared" si="223"/>
+        <f t="shared" si="226"/>
         <v>588</v>
       </c>
       <c r="XR10" s="49"/>
@@ -35554,7 +36186,7 @@
         <v>1.68</v>
       </c>
       <c r="XZ10" s="48">
-        <f t="shared" si="224"/>
+        <f t="shared" si="227"/>
         <v>477.12</v>
       </c>
       <c r="YA10" s="49"/>
@@ -35570,7 +36202,7 @@
         <v>1.68</v>
       </c>
       <c r="YI10" s="48">
-        <f t="shared" si="225"/>
+        <f t="shared" si="228"/>
         <v>383.03999999999996</v>
       </c>
       <c r="YJ10" s="49"/>
@@ -35586,7 +36218,7 @@
         <v>1.68</v>
       </c>
       <c r="YR10" s="48">
-        <f t="shared" si="226"/>
+        <f t="shared" si="229"/>
         <v>270.48</v>
       </c>
       <c r="YS10" s="49"/>
@@ -35602,14 +36234,30 @@
         <v>1.68</v>
       </c>
       <c r="ZA10" s="48">
-        <f t="shared" si="227"/>
+        <f t="shared" si="230"/>
         <v>772.8</v>
       </c>
       <c r="ZB10" s="49"/>
       <c r="ZC10" s="306"/>
       <c r="ZD10" s="75"/>
-    </row>
-    <row r="11" spans="2:680" x14ac:dyDescent="0.25">
+      <c r="ZF10" s="278"/>
+      <c r="ZG10" s="278"/>
+      <c r="ZH10" s="46">
+        <f>ZH11-ZH9</f>
+        <v>-140</v>
+      </c>
+      <c r="ZI10" s="48">
+        <v>1.68</v>
+      </c>
+      <c r="ZJ10" s="48">
+        <f t="shared" si="231"/>
+        <v>-235.2</v>
+      </c>
+      <c r="ZK10" s="49"/>
+      <c r="ZL10" s="306"/>
+      <c r="ZM10" s="75"/>
+    </row>
+    <row r="11" spans="2:689" x14ac:dyDescent="0.25">
       <c r="B11" s="46">
         <v>402780</v>
       </c>
@@ -35708,7 +36356,7 @@
       <c r="AX11" s="49"/>
       <c r="AY11" s="99"/>
       <c r="AZ11" s="99">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="BA11" s="67"/>
@@ -35727,7 +36375,7 @@
       <c r="BF11" s="49"/>
       <c r="BG11" s="99"/>
       <c r="BH11" s="99">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="BI11" s="67"/>
@@ -35746,7 +36394,7 @@
       <c r="BN11" s="49"/>
       <c r="BO11" s="99"/>
       <c r="BP11" s="99">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0</v>
       </c>
       <c r="BQ11" s="67"/>
@@ -35765,7 +36413,7 @@
       <c r="BV11" s="49"/>
       <c r="BW11" s="99"/>
       <c r="BX11" s="99">
-        <f t="shared" si="228"/>
+        <f t="shared" si="232"/>
         <v>0</v>
       </c>
       <c r="BY11" s="67"/>
@@ -35784,7 +36432,7 @@
       <c r="CD11" s="49"/>
       <c r="CE11" s="99"/>
       <c r="CF11" s="99">
-        <f t="shared" si="229"/>
+        <f t="shared" si="233"/>
         <v>0</v>
       </c>
       <c r="CI11" s="67"/>
@@ -35803,7 +36451,7 @@
       <c r="CN11" s="49"/>
       <c r="CO11" s="99"/>
       <c r="CP11" s="99">
-        <f t="shared" si="230"/>
+        <f t="shared" si="234"/>
         <v>0</v>
       </c>
       <c r="CQ11" s="67"/>
@@ -35822,7 +36470,7 @@
       <c r="CV11" s="49"/>
       <c r="CW11" s="99"/>
       <c r="CX11" s="99">
-        <f t="shared" si="231"/>
+        <f t="shared" si="235"/>
         <v>0</v>
       </c>
       <c r="CY11" s="67"/>
@@ -35841,7 +36489,7 @@
       <c r="DD11" s="49"/>
       <c r="DE11" s="99"/>
       <c r="DF11" s="142">
-        <f t="shared" si="232"/>
+        <f t="shared" si="236"/>
         <v>0</v>
       </c>
       <c r="DG11" s="67"/>
@@ -35860,7 +36508,7 @@
       <c r="DL11" s="49"/>
       <c r="DM11" s="128"/>
       <c r="DN11" s="140">
-        <f t="shared" si="233"/>
+        <f t="shared" si="237"/>
         <v>0</v>
       </c>
       <c r="DO11" s="67"/>
@@ -35879,7 +36527,7 @@
       <c r="DT11" s="49"/>
       <c r="DU11" s="128"/>
       <c r="DV11" s="140">
-        <f t="shared" si="234"/>
+        <f t="shared" si="238"/>
         <v>0</v>
       </c>
       <c r="DW11" s="67"/>
@@ -35898,7 +36546,7 @@
       <c r="EB11" s="49"/>
       <c r="EC11" s="128"/>
       <c r="ED11" s="140">
-        <f t="shared" si="235"/>
+        <f t="shared" si="239"/>
         <v>0</v>
       </c>
       <c r="EE11" s="67"/>
@@ -35917,7 +36565,7 @@
       <c r="EJ11" s="49"/>
       <c r="EK11" s="128"/>
       <c r="EL11" s="140">
-        <f t="shared" si="236"/>
+        <f t="shared" si="240"/>
         <v>0</v>
       </c>
       <c r="EM11" s="67"/>
@@ -35936,7 +36584,7 @@
       <c r="ER11" s="49"/>
       <c r="ES11" s="128"/>
       <c r="ET11" s="140">
-        <f t="shared" si="237"/>
+        <f t="shared" si="241"/>
         <v>0</v>
       </c>
       <c r="EU11" s="67"/>
@@ -35955,7 +36603,7 @@
       <c r="EZ11" s="49"/>
       <c r="FA11" s="128"/>
       <c r="FB11" s="140">
-        <f t="shared" si="238"/>
+        <f t="shared" si="242"/>
         <v>0</v>
       </c>
       <c r="FC11" s="67"/>
@@ -35974,7 +36622,7 @@
       <c r="FH11" s="49"/>
       <c r="FI11" s="128"/>
       <c r="FJ11" s="140">
-        <f t="shared" si="239"/>
+        <f t="shared" si="243"/>
         <v>0</v>
       </c>
       <c r="FK11" s="67"/>
@@ -35993,7 +36641,7 @@
       <c r="FP11" s="49"/>
       <c r="FQ11" s="128"/>
       <c r="FR11" s="182">
-        <f t="shared" si="240"/>
+        <f t="shared" si="244"/>
         <v>0</v>
       </c>
       <c r="FS11" s="67"/>
@@ -36012,7 +36660,7 @@
       <c r="FX11" s="49"/>
       <c r="FY11" s="128"/>
       <c r="FZ11" s="182">
-        <f t="shared" si="241"/>
+        <f t="shared" si="245"/>
         <v>0</v>
       </c>
       <c r="GA11" s="67"/>
@@ -36025,13 +36673,13 @@
         <v>1.68</v>
       </c>
       <c r="GE11" s="48">
-        <f t="shared" si="170"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="GF11" s="49"/>
       <c r="GG11" s="128"/>
       <c r="GH11" s="182">
-        <f t="shared" si="242"/>
+        <f t="shared" si="246"/>
         <v>0</v>
       </c>
       <c r="GI11" s="67"/>
@@ -36044,13 +36692,13 @@
         <v>1.68</v>
       </c>
       <c r="GM11" s="48">
-        <f t="shared" si="171"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="GN11" s="49"/>
       <c r="GO11" s="128"/>
       <c r="GP11" s="182">
-        <f t="shared" si="243"/>
+        <f t="shared" si="247"/>
         <v>0</v>
       </c>
       <c r="GQ11" s="67"/>
@@ -36063,13 +36711,13 @@
         <v>1.68</v>
       </c>
       <c r="GU11" s="48">
-        <f t="shared" si="172"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="GV11" s="49"/>
       <c r="GW11" s="128"/>
       <c r="GX11" s="182">
-        <f t="shared" si="244"/>
+        <f t="shared" si="248"/>
         <v>0</v>
       </c>
       <c r="GY11" s="67"/>
@@ -36082,13 +36730,13 @@
         <v>1.68</v>
       </c>
       <c r="HC11" s="48">
-        <f t="shared" si="173"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="HD11" s="49"/>
       <c r="HE11" s="128"/>
       <c r="HF11" s="182">
-        <f t="shared" si="245"/>
+        <f t="shared" si="249"/>
         <v>0</v>
       </c>
       <c r="HG11" s="67"/>
@@ -36101,13 +36749,13 @@
         <v>1.68</v>
       </c>
       <c r="HK11" s="48">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="HL11" s="49"/>
       <c r="HM11" s="128"/>
       <c r="HN11" s="182">
-        <f t="shared" si="246"/>
+        <f t="shared" si="250"/>
         <v>0</v>
       </c>
       <c r="HO11" s="67"/>
@@ -36120,13 +36768,13 @@
         <v>1.68</v>
       </c>
       <c r="HS11" s="48">
-        <f t="shared" si="175"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="HT11" s="49"/>
       <c r="HU11" s="128"/>
       <c r="HV11" s="182">
-        <f t="shared" si="247"/>
+        <f t="shared" si="251"/>
         <v>0</v>
       </c>
       <c r="HW11" s="67"/>
@@ -36139,13 +36787,13 @@
         <v>1.68</v>
       </c>
       <c r="IA11" s="48">
-        <f t="shared" si="176"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
       <c r="IB11" s="49"/>
       <c r="IC11" s="128"/>
       <c r="ID11" s="182">
-        <f t="shared" si="248"/>
+        <f t="shared" si="252"/>
         <v>0</v>
       </c>
       <c r="IE11" s="67"/>
@@ -36158,13 +36806,13 @@
         <v>1.68</v>
       </c>
       <c r="II11" s="48">
-        <f t="shared" si="177"/>
+        <f t="shared" si="180"/>
         <v>0</v>
       </c>
       <c r="IJ11" s="49"/>
       <c r="IK11" s="128"/>
       <c r="IL11" s="182">
-        <f t="shared" si="249"/>
+        <f t="shared" si="253"/>
         <v>0</v>
       </c>
       <c r="IM11" s="67"/>
@@ -36177,203 +36825,203 @@
         <v>1.68</v>
       </c>
       <c r="IQ11" s="48">
-        <f t="shared" si="178"/>
+        <f t="shared" si="181"/>
         <v>0</v>
       </c>
       <c r="IR11" s="49"/>
       <c r="IS11" s="128"/>
       <c r="IT11" s="182">
-        <f t="shared" si="250"/>
+        <f t="shared" si="254"/>
         <v>0</v>
       </c>
       <c r="IU11" s="67"/>
       <c r="IV11" s="67"/>
       <c r="IW11" s="46">
-        <f t="shared" ref="IW11:IW14" si="276">IU11-IV11</f>
+        <f t="shared" ref="IW11:IW14" si="280">IU11-IV11</f>
         <v>0</v>
       </c>
       <c r="IX11" s="48">
         <v>1.68</v>
       </c>
       <c r="IY11" s="48">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>0</v>
       </c>
       <c r="IZ11" s="49"/>
       <c r="JA11" s="128"/>
       <c r="JB11" s="182">
-        <f t="shared" si="251"/>
+        <f t="shared" si="255"/>
         <v>0</v>
       </c>
       <c r="JC11" s="67"/>
       <c r="JD11" s="67"/>
       <c r="JE11" s="46">
-        <f t="shared" ref="JE11:JE14" si="277">JC11-JD11</f>
+        <f t="shared" ref="JE11:JE14" si="281">JC11-JD11</f>
         <v>0</v>
       </c>
       <c r="JF11" s="48">
         <v>1.68</v>
       </c>
       <c r="JG11" s="48">
-        <f t="shared" si="180"/>
+        <f t="shared" si="183"/>
         <v>0</v>
       </c>
       <c r="JH11" s="49"/>
       <c r="JI11" s="128"/>
       <c r="JJ11" s="231">
-        <f t="shared" si="252"/>
+        <f t="shared" si="256"/>
         <v>0</v>
       </c>
       <c r="JK11" s="67"/>
       <c r="JL11" s="67"/>
       <c r="JM11" s="46">
-        <f t="shared" ref="JM11:JM14" si="278">JK11-JL11</f>
+        <f t="shared" ref="JM11:JM14" si="282">JK11-JL11</f>
         <v>0</v>
       </c>
       <c r="JN11" s="48">
         <v>1.68</v>
       </c>
       <c r="JO11" s="48">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>0</v>
       </c>
       <c r="JP11" s="49"/>
       <c r="JQ11" s="128"/>
       <c r="JR11" s="231">
-        <f t="shared" si="253"/>
+        <f t="shared" si="257"/>
         <v>0</v>
       </c>
       <c r="JS11" s="67"/>
       <c r="JT11" s="67"/>
       <c r="JU11" s="46">
-        <f t="shared" ref="JU11:JU14" si="279">JS11-JT11</f>
+        <f t="shared" ref="JU11:JU14" si="283">JS11-JT11</f>
         <v>0</v>
       </c>
       <c r="JV11" s="48">
         <v>1.68</v>
       </c>
       <c r="JW11" s="48">
-        <f t="shared" si="182"/>
+        <f t="shared" si="185"/>
         <v>0</v>
       </c>
       <c r="JX11" s="49"/>
       <c r="JY11" s="128"/>
       <c r="JZ11" s="231">
-        <f t="shared" si="254"/>
+        <f t="shared" si="258"/>
         <v>0</v>
       </c>
       <c r="KA11" s="67"/>
       <c r="KB11" s="67"/>
       <c r="KC11" s="46">
-        <f t="shared" ref="KC11:KC14" si="280">KA11-KB11</f>
+        <f t="shared" ref="KC11:KC14" si="284">KA11-KB11</f>
         <v>0</v>
       </c>
       <c r="KD11" s="48">
         <v>1.68</v>
       </c>
       <c r="KE11" s="48">
-        <f t="shared" si="183"/>
+        <f t="shared" si="186"/>
         <v>0</v>
       </c>
       <c r="KF11" s="49"/>
       <c r="KG11" s="128"/>
       <c r="KH11" s="231">
-        <f t="shared" si="255"/>
+        <f t="shared" si="259"/>
         <v>0</v>
       </c>
       <c r="KI11" s="67"/>
       <c r="KJ11" s="67"/>
       <c r="KK11" s="46">
-        <f t="shared" ref="KK11:KK14" si="281">KI11-KJ11</f>
+        <f t="shared" ref="KK11:KK14" si="285">KI11-KJ11</f>
         <v>0</v>
       </c>
       <c r="KL11" s="48">
         <v>1.68</v>
       </c>
       <c r="KM11" s="48">
-        <f t="shared" si="184"/>
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
       <c r="KN11" s="49"/>
       <c r="KO11" s="128"/>
       <c r="KP11" s="231">
-        <f t="shared" si="256"/>
+        <f t="shared" si="260"/>
         <v>0</v>
       </c>
       <c r="KQ11" s="67"/>
       <c r="KR11" s="67"/>
       <c r="KS11" s="46">
-        <f t="shared" ref="KS11:KS14" si="282">KQ11-KR11</f>
+        <f t="shared" ref="KS11:KS14" si="286">KQ11-KR11</f>
         <v>0</v>
       </c>
       <c r="KT11" s="48">
         <v>1.68</v>
       </c>
       <c r="KU11" s="48">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="KV11" s="49"/>
       <c r="KW11" s="128"/>
       <c r="KX11" s="231">
-        <f t="shared" si="257"/>
+        <f t="shared" si="261"/>
         <v>0</v>
       </c>
       <c r="KY11" s="67"/>
       <c r="KZ11" s="67"/>
       <c r="LA11" s="46">
-        <f t="shared" ref="LA11:LA14" si="283">KY11-KZ11</f>
+        <f t="shared" ref="LA11:LA14" si="287">KY11-KZ11</f>
         <v>0</v>
       </c>
       <c r="LB11" s="48">
         <v>1.68</v>
       </c>
       <c r="LC11" s="48">
-        <f t="shared" si="186"/>
+        <f t="shared" si="189"/>
         <v>0</v>
       </c>
       <c r="LD11" s="49"/>
       <c r="LE11" s="128"/>
       <c r="LF11" s="231">
-        <f t="shared" si="258"/>
+        <f t="shared" si="262"/>
         <v>0</v>
       </c>
       <c r="LG11" s="67"/>
       <c r="LH11" s="67"/>
       <c r="LI11" s="46">
-        <f t="shared" ref="LI11:LI14" si="284">LG11-LH11</f>
+        <f t="shared" ref="LI11:LI14" si="288">LG11-LH11</f>
         <v>0</v>
       </c>
       <c r="LJ11" s="48">
         <v>1.68</v>
       </c>
       <c r="LK11" s="48">
-        <f t="shared" si="187"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="LL11" s="49"/>
       <c r="LM11" s="128"/>
       <c r="LN11" s="231">
-        <f t="shared" si="259"/>
+        <f t="shared" si="263"/>
         <v>0</v>
       </c>
       <c r="LO11" s="67"/>
       <c r="LP11" s="67"/>
       <c r="LQ11" s="46">
-        <f t="shared" ref="LQ11:LQ14" si="285">LO11-LP11</f>
+        <f t="shared" ref="LQ11:LQ14" si="289">LO11-LP11</f>
         <v>0</v>
       </c>
       <c r="LR11" s="48">
         <v>1.68</v>
       </c>
       <c r="LS11" s="48">
-        <f t="shared" ref="LS11:LS14" si="286">LQ11*LR11</f>
+        <f t="shared" ref="LS11:LS14" si="290">LQ11*LR11</f>
         <v>0</v>
       </c>
       <c r="LT11" s="49"/>
       <c r="LU11" s="128"/>
       <c r="LV11" s="231">
-        <f t="shared" si="260"/>
+        <f t="shared" si="264"/>
         <v>0</v>
       </c>
       <c r="LW11" s="278"/>
@@ -36384,7 +37032,7 @@
       <c r="MB11" s="49"/>
       <c r="MC11" s="231"/>
       <c r="MD11" s="250">
-        <f t="shared" si="261"/>
+        <f t="shared" si="265"/>
         <v>0</v>
       </c>
       <c r="MF11" s="278"/>
@@ -36395,7 +37043,7 @@
       <c r="MK11" s="49"/>
       <c r="ML11" s="231"/>
       <c r="MM11" s="250">
-        <f t="shared" si="262"/>
+        <f t="shared" si="266"/>
         <v>0</v>
       </c>
       <c r="MN11" s="278"/>
@@ -36406,7 +37054,7 @@
       <c r="MS11" s="49"/>
       <c r="MT11" s="231"/>
       <c r="MU11" s="250">
-        <f t="shared" si="263"/>
+        <f t="shared" si="267"/>
         <v>0</v>
       </c>
       <c r="MV11" s="278"/>
@@ -36417,7 +37065,7 @@
       <c r="NA11" s="49"/>
       <c r="NB11" s="231"/>
       <c r="NC11" s="250">
-        <f t="shared" si="264"/>
+        <f t="shared" si="268"/>
         <v>0</v>
       </c>
       <c r="ND11" s="278"/>
@@ -36428,7 +37076,7 @@
       <c r="NI11" s="49"/>
       <c r="NJ11" s="231"/>
       <c r="NK11" s="250">
-        <f t="shared" si="265"/>
+        <f t="shared" si="269"/>
         <v>0</v>
       </c>
       <c r="NL11" s="278"/>
@@ -36439,7 +37087,7 @@
       <c r="NQ11" s="49"/>
       <c r="NR11" s="231"/>
       <c r="NS11" s="250">
-        <f t="shared" si="266"/>
+        <f t="shared" si="270"/>
         <v>0</v>
       </c>
       <c r="NT11" s="278"/>
@@ -36450,7 +37098,7 @@
       <c r="NY11" s="49"/>
       <c r="NZ11" s="231"/>
       <c r="OA11" s="250">
-        <f t="shared" si="267"/>
+        <f t="shared" si="271"/>
         <v>0</v>
       </c>
       <c r="OB11" s="278"/>
@@ -36461,7 +37109,7 @@
       <c r="OG11" s="49"/>
       <c r="OH11" s="231"/>
       <c r="OI11" s="250">
-        <f t="shared" si="268"/>
+        <f t="shared" si="272"/>
         <v>0</v>
       </c>
       <c r="OJ11" s="278"/>
@@ -36472,7 +37120,7 @@
       <c r="OO11" s="49"/>
       <c r="OP11" s="231"/>
       <c r="OQ11" s="250">
-        <f t="shared" si="269"/>
+        <f t="shared" si="273"/>
         <v>0</v>
       </c>
       <c r="OR11" s="278"/>
@@ -36483,7 +37131,7 @@
       <c r="OW11" s="49"/>
       <c r="OX11" s="231"/>
       <c r="OY11" s="250">
-        <f t="shared" si="271"/>
+        <f t="shared" si="275"/>
         <v>0</v>
       </c>
       <c r="OZ11" s="278"/>
@@ -36497,7 +37145,7 @@
       <c r="PE11" s="49"/>
       <c r="PF11" s="231"/>
       <c r="PG11" s="250">
-        <f t="shared" si="272"/>
+        <f t="shared" si="276"/>
         <v>0</v>
       </c>
       <c r="PH11" s="278"/>
@@ -36511,7 +37159,7 @@
       <c r="PM11" s="49"/>
       <c r="PN11" s="231"/>
       <c r="PO11" s="250">
-        <f t="shared" si="274"/>
+        <f t="shared" si="278"/>
         <v>0</v>
       </c>
       <c r="PP11" s="278"/>
@@ -36525,7 +37173,7 @@
       <c r="PU11" s="49"/>
       <c r="PV11" s="231"/>
       <c r="PW11" s="250">
-        <f t="shared" si="275"/>
+        <f t="shared" si="279"/>
         <v>0</v>
       </c>
       <c r="PY11" s="278"/>
@@ -36935,8 +37583,24 @@
       <c r="ZB11" s="49"/>
       <c r="ZC11" s="306"/>
       <c r="ZD11" s="75"/>
-    </row>
-    <row r="12" spans="2:680" x14ac:dyDescent="0.25">
+      <c r="ZF11" s="278"/>
+      <c r="ZG11" s="278"/>
+      <c r="ZH11" s="286">
+        <f>ZF9-ZG9</f>
+        <v>110</v>
+      </c>
+      <c r="ZI11" s="48">
+        <v>2.64</v>
+      </c>
+      <c r="ZJ11" s="300">
+        <f>ZH11*ZI11</f>
+        <v>290.40000000000003</v>
+      </c>
+      <c r="ZK11" s="49"/>
+      <c r="ZL11" s="306"/>
+      <c r="ZM11" s="75"/>
+    </row>
+    <row r="12" spans="2:689" x14ac:dyDescent="0.25">
       <c r="B12" s="46">
         <v>7046</v>
       </c>
@@ -37045,7 +37709,7 @@
         <v>15</v>
       </c>
       <c r="AZ12" s="99">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>15</v>
       </c>
       <c r="BA12" s="67"/>
@@ -37066,7 +37730,7 @@
         <v>15</v>
       </c>
       <c r="BH12" s="99">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>15</v>
       </c>
       <c r="BI12" s="67"/>
@@ -37087,7 +37751,7 @@
         <v>15</v>
       </c>
       <c r="BP12" s="99">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>15</v>
       </c>
       <c r="BQ12" s="67"/>
@@ -37376,7 +38040,7 @@
         <v>1.68</v>
       </c>
       <c r="GE12" s="48">
-        <f t="shared" si="170"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="GF12" s="49"/>
@@ -37396,7 +38060,7 @@
         <v>1.68</v>
       </c>
       <c r="GM12" s="48">
-        <f t="shared" si="171"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="GN12" s="49"/>
@@ -37416,7 +38080,7 @@
         <v>1.68</v>
       </c>
       <c r="GU12" s="48">
-        <f t="shared" si="172"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="GV12" s="49"/>
@@ -37436,7 +38100,7 @@
         <v>1.68</v>
       </c>
       <c r="HC12" s="48">
-        <f t="shared" si="173"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="HD12" s="49"/>
@@ -37456,7 +38120,7 @@
         <v>1.68</v>
       </c>
       <c r="HK12" s="48">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="HL12" s="49"/>
@@ -37476,7 +38140,7 @@
         <v>1.68</v>
       </c>
       <c r="HS12" s="48">
-        <f t="shared" si="175"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="HT12" s="49"/>
@@ -37496,7 +38160,7 @@
         <v>1.68</v>
       </c>
       <c r="IA12" s="48">
-        <f t="shared" si="176"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
       <c r="IB12" s="49"/>
@@ -37516,7 +38180,7 @@
         <v>1.68</v>
       </c>
       <c r="II12" s="48">
-        <f t="shared" si="177"/>
+        <f t="shared" si="180"/>
         <v>0</v>
       </c>
       <c r="IJ12" s="49"/>
@@ -37536,7 +38200,7 @@
         <v>1.68</v>
       </c>
       <c r="IQ12" s="48">
-        <f t="shared" si="178"/>
+        <f t="shared" si="181"/>
         <v>0</v>
       </c>
       <c r="IR12" s="49"/>
@@ -37549,14 +38213,14 @@
       <c r="IU12" s="67"/>
       <c r="IV12" s="67"/>
       <c r="IW12" s="46">
-        <f t="shared" si="276"/>
+        <f t="shared" si="280"/>
         <v>0</v>
       </c>
       <c r="IX12" s="48">
         <v>1.68</v>
       </c>
       <c r="IY12" s="48">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>0</v>
       </c>
       <c r="IZ12" s="49"/>
@@ -37569,14 +38233,14 @@
       <c r="JC12" s="67"/>
       <c r="JD12" s="67"/>
       <c r="JE12" s="46">
-        <f t="shared" si="277"/>
+        <f t="shared" si="281"/>
         <v>0</v>
       </c>
       <c r="JF12" s="48">
         <v>1.68</v>
       </c>
       <c r="JG12" s="48">
-        <f t="shared" si="180"/>
+        <f t="shared" si="183"/>
         <v>0</v>
       </c>
       <c r="JH12" s="49"/>
@@ -37589,14 +38253,14 @@
       <c r="JK12" s="67"/>
       <c r="JL12" s="67"/>
       <c r="JM12" s="46">
-        <f t="shared" si="278"/>
+        <f t="shared" si="282"/>
         <v>0</v>
       </c>
       <c r="JN12" s="48">
         <v>1.68</v>
       </c>
       <c r="JO12" s="48">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>0</v>
       </c>
       <c r="JP12" s="49"/>
@@ -37609,14 +38273,14 @@
       <c r="JS12" s="67"/>
       <c r="JT12" s="67"/>
       <c r="JU12" s="46">
-        <f t="shared" si="279"/>
+        <f t="shared" si="283"/>
         <v>0</v>
       </c>
       <c r="JV12" s="48">
         <v>1.68</v>
       </c>
       <c r="JW12" s="48">
-        <f t="shared" si="182"/>
+        <f t="shared" si="185"/>
         <v>0</v>
       </c>
       <c r="JX12" s="49"/>
@@ -37629,14 +38293,14 @@
       <c r="KA12" s="67"/>
       <c r="KB12" s="67"/>
       <c r="KC12" s="46">
-        <f t="shared" si="280"/>
+        <f t="shared" si="284"/>
         <v>0</v>
       </c>
       <c r="KD12" s="48">
         <v>1.68</v>
       </c>
       <c r="KE12" s="48">
-        <f t="shared" si="183"/>
+        <f t="shared" si="186"/>
         <v>0</v>
       </c>
       <c r="KF12" s="49"/>
@@ -37649,14 +38313,14 @@
       <c r="KI12" s="67"/>
       <c r="KJ12" s="67"/>
       <c r="KK12" s="46">
-        <f t="shared" si="281"/>
+        <f t="shared" si="285"/>
         <v>0</v>
       </c>
       <c r="KL12" s="48">
         <v>1.68</v>
       </c>
       <c r="KM12" s="48">
-        <f t="shared" si="184"/>
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
       <c r="KN12" s="49"/>
@@ -37669,14 +38333,14 @@
       <c r="KQ12" s="67"/>
       <c r="KR12" s="67"/>
       <c r="KS12" s="46">
-        <f t="shared" si="282"/>
+        <f t="shared" si="286"/>
         <v>0</v>
       </c>
       <c r="KT12" s="48">
         <v>1.68</v>
       </c>
       <c r="KU12" s="48">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="KV12" s="49"/>
@@ -37689,14 +38353,14 @@
       <c r="KY12" s="67"/>
       <c r="KZ12" s="67"/>
       <c r="LA12" s="46">
-        <f t="shared" si="283"/>
+        <f t="shared" si="287"/>
         <v>0</v>
       </c>
       <c r="LB12" s="48">
         <v>1.68</v>
       </c>
       <c r="LC12" s="48">
-        <f t="shared" si="186"/>
+        <f t="shared" si="189"/>
         <v>0</v>
       </c>
       <c r="LD12" s="49"/>
@@ -37709,14 +38373,14 @@
       <c r="LG12" s="67"/>
       <c r="LH12" s="67"/>
       <c r="LI12" s="46">
-        <f t="shared" si="284"/>
+        <f t="shared" si="288"/>
         <v>0</v>
       </c>
       <c r="LJ12" s="48">
         <v>1.68</v>
       </c>
       <c r="LK12" s="48">
-        <f t="shared" si="187"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="LL12" s="49"/>
@@ -37729,14 +38393,14 @@
       <c r="LO12" s="67"/>
       <c r="LP12" s="67"/>
       <c r="LQ12" s="46">
-        <f t="shared" si="285"/>
+        <f t="shared" si="289"/>
         <v>0</v>
       </c>
       <c r="LR12" s="48">
         <v>1.68</v>
       </c>
       <c r="LS12" s="48">
-        <f t="shared" si="286"/>
+        <f t="shared" si="290"/>
         <v>0</v>
       </c>
       <c r="LT12" s="49"/>
@@ -38243,8 +38907,21 @@
         <f>ZC12</f>
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="2:680" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="ZF12" s="278"/>
+      <c r="ZG12" s="278"/>
+      <c r="ZH12" s="46"/>
+      <c r="ZI12" s="48"/>
+      <c r="ZJ12" s="48"/>
+      <c r="ZK12" s="49"/>
+      <c r="ZL12" s="306">
+        <v>35</v>
+      </c>
+      <c r="ZM12" s="324">
+        <f>ZL12</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="2:689" ht="29.25" x14ac:dyDescent="0.25">
       <c r="B13" s="46">
         <v>21502</v>
       </c>
@@ -38345,7 +39022,7 @@
       <c r="AX13" s="49"/>
       <c r="AY13" s="99"/>
       <c r="AZ13" s="99">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="BA13" s="67"/>
@@ -38364,7 +39041,7 @@
       <c r="BF13" s="49"/>
       <c r="BG13" s="99"/>
       <c r="BH13" s="99">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="BI13" s="67"/>
@@ -38383,7 +39060,7 @@
       <c r="BN13" s="49"/>
       <c r="BO13" s="99"/>
       <c r="BP13" s="99">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0</v>
       </c>
       <c r="BQ13" s="67"/>
@@ -38402,7 +39079,7 @@
       <c r="BV13" s="49"/>
       <c r="BW13" s="99"/>
       <c r="BX13" s="99">
-        <f t="shared" si="228"/>
+        <f t="shared" si="232"/>
         <v>0</v>
       </c>
       <c r="BY13" s="67"/>
@@ -38625,7 +39302,7 @@
         <v>1.68</v>
       </c>
       <c r="GE13" s="48">
-        <f t="shared" si="170"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="GF13" s="49"/>
@@ -38641,7 +39318,7 @@
         <v>1.68</v>
       </c>
       <c r="GM13" s="48">
-        <f t="shared" si="171"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="GN13" s="49"/>
@@ -38657,7 +39334,7 @@
         <v>1.68</v>
       </c>
       <c r="GU13" s="48">
-        <f t="shared" si="172"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="GV13" s="49"/>
@@ -38673,7 +39350,7 @@
         <v>1.68</v>
       </c>
       <c r="HC13" s="48">
-        <f t="shared" si="173"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="HD13" s="49"/>
@@ -38689,7 +39366,7 @@
         <v>1.68</v>
       </c>
       <c r="HK13" s="48">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="HL13" s="49"/>
@@ -38705,7 +39382,7 @@
         <v>1.68</v>
       </c>
       <c r="HS13" s="48">
-        <f t="shared" si="175"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="HT13" s="49"/>
@@ -38721,7 +39398,7 @@
         <v>1.68</v>
       </c>
       <c r="IA13" s="48">
-        <f t="shared" si="176"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
       <c r="IB13" s="49"/>
@@ -38737,7 +39414,7 @@
         <v>1.68</v>
       </c>
       <c r="II13" s="48">
-        <f t="shared" si="177"/>
+        <f t="shared" si="180"/>
         <v>0</v>
       </c>
       <c r="IJ13" s="49"/>
@@ -38753,7 +39430,7 @@
         <v>1.68</v>
       </c>
       <c r="IQ13" s="48">
-        <f t="shared" si="178"/>
+        <f t="shared" si="181"/>
         <v>0</v>
       </c>
       <c r="IR13" s="49"/>
@@ -38762,14 +39439,14 @@
       <c r="IU13" s="67"/>
       <c r="IV13" s="67"/>
       <c r="IW13" s="46">
-        <f t="shared" si="276"/>
+        <f t="shared" si="280"/>
         <v>0</v>
       </c>
       <c r="IX13" s="48">
         <v>1.68</v>
       </c>
       <c r="IY13" s="48">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>0</v>
       </c>
       <c r="IZ13" s="49"/>
@@ -38778,14 +39455,14 @@
       <c r="JC13" s="67"/>
       <c r="JD13" s="67"/>
       <c r="JE13" s="46">
-        <f t="shared" si="277"/>
+        <f t="shared" si="281"/>
         <v>0</v>
       </c>
       <c r="JF13" s="48">
         <v>1.68</v>
       </c>
       <c r="JG13" s="48">
-        <f t="shared" si="180"/>
+        <f t="shared" si="183"/>
         <v>0</v>
       </c>
       <c r="JH13" s="49"/>
@@ -38794,14 +39471,14 @@
       <c r="JK13" s="67"/>
       <c r="JL13" s="67"/>
       <c r="JM13" s="46">
-        <f t="shared" si="278"/>
+        <f t="shared" si="282"/>
         <v>0</v>
       </c>
       <c r="JN13" s="48">
         <v>1.68</v>
       </c>
       <c r="JO13" s="48">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>0</v>
       </c>
       <c r="JP13" s="49"/>
@@ -38810,14 +39487,14 @@
       <c r="JS13" s="67"/>
       <c r="JT13" s="67"/>
       <c r="JU13" s="46">
-        <f t="shared" si="279"/>
+        <f t="shared" si="283"/>
         <v>0</v>
       </c>
       <c r="JV13" s="48">
         <v>1.68</v>
       </c>
       <c r="JW13" s="48">
-        <f t="shared" si="182"/>
+        <f t="shared" si="185"/>
         <v>0</v>
       </c>
       <c r="JX13" s="49"/>
@@ -38826,14 +39503,14 @@
       <c r="KA13" s="67"/>
       <c r="KB13" s="67"/>
       <c r="KC13" s="46">
-        <f t="shared" si="280"/>
+        <f t="shared" si="284"/>
         <v>0</v>
       </c>
       <c r="KD13" s="48">
         <v>1.68</v>
       </c>
       <c r="KE13" s="48">
-        <f t="shared" si="183"/>
+        <f t="shared" si="186"/>
         <v>0</v>
       </c>
       <c r="KF13" s="49"/>
@@ -38842,14 +39519,14 @@
       <c r="KI13" s="67"/>
       <c r="KJ13" s="67"/>
       <c r="KK13" s="46">
-        <f t="shared" si="281"/>
+        <f t="shared" si="285"/>
         <v>0</v>
       </c>
       <c r="KL13" s="48">
         <v>1.68</v>
       </c>
       <c r="KM13" s="48">
-        <f t="shared" si="184"/>
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
       <c r="KN13" s="49"/>
@@ -38858,14 +39535,14 @@
       <c r="KQ13" s="67"/>
       <c r="KR13" s="67"/>
       <c r="KS13" s="46">
-        <f t="shared" si="282"/>
+        <f t="shared" si="286"/>
         <v>0</v>
       </c>
       <c r="KT13" s="48">
         <v>1.68</v>
       </c>
       <c r="KU13" s="48">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="KV13" s="49"/>
@@ -38874,14 +39551,14 @@
       <c r="KY13" s="67"/>
       <c r="KZ13" s="67"/>
       <c r="LA13" s="46">
-        <f t="shared" si="283"/>
+        <f t="shared" si="287"/>
         <v>0</v>
       </c>
       <c r="LB13" s="48">
         <v>1.68</v>
       </c>
       <c r="LC13" s="48">
-        <f t="shared" si="186"/>
+        <f t="shared" si="189"/>
         <v>0</v>
       </c>
       <c r="LD13" s="49"/>
@@ -38890,14 +39567,14 @@
       <c r="LG13" s="67"/>
       <c r="LH13" s="67"/>
       <c r="LI13" s="46">
-        <f t="shared" si="284"/>
+        <f t="shared" si="288"/>
         <v>0</v>
       </c>
       <c r="LJ13" s="48">
         <v>1.68</v>
       </c>
       <c r="LK13" s="48">
-        <f t="shared" si="187"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="LL13" s="49"/>
@@ -38906,14 +39583,14 @@
       <c r="LO13" s="67"/>
       <c r="LP13" s="67"/>
       <c r="LQ13" s="46">
-        <f t="shared" si="285"/>
+        <f t="shared" si="289"/>
         <v>0</v>
       </c>
       <c r="LR13" s="48">
         <v>1.68</v>
       </c>
       <c r="LS13" s="48">
-        <f t="shared" si="286"/>
+        <f t="shared" si="290"/>
         <v>0</v>
       </c>
       <c r="LT13" s="49"/>
@@ -39239,8 +39916,16 @@
       <c r="ZB13" s="49"/>
       <c r="ZC13" s="306"/>
       <c r="ZD13" s="75"/>
-    </row>
-    <row r="14" spans="2:680" x14ac:dyDescent="0.25">
+      <c r="ZF13" s="278"/>
+      <c r="ZG13" s="278"/>
+      <c r="ZH13" s="46"/>
+      <c r="ZI13" s="48"/>
+      <c r="ZJ13" s="48"/>
+      <c r="ZK13" s="49"/>
+      <c r="ZL13" s="306"/>
+      <c r="ZM13" s="75"/>
+    </row>
+    <row r="14" spans="2:689" x14ac:dyDescent="0.25">
       <c r="B14" s="46">
         <v>330152984</v>
       </c>
@@ -39374,7 +40059,7 @@
         <v>118.2843</v>
       </c>
       <c r="AZ14" s="99">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>118.2843</v>
       </c>
       <c r="BA14" s="67">
@@ -39400,7 +40085,7 @@
         <v>90.452700000000007</v>
       </c>
       <c r="BH14" s="99">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>90.452700000000007</v>
       </c>
       <c r="BI14" s="67">
@@ -39426,7 +40111,7 @@
         <v>118.2843</v>
       </c>
       <c r="BP14" s="99">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>118.2843</v>
       </c>
       <c r="BQ14" s="67">
@@ -39452,7 +40137,7 @@
         <v>132.20010000000002</v>
       </c>
       <c r="BX14" s="99">
-        <f t="shared" si="228"/>
+        <f t="shared" si="232"/>
         <v>132.20010000000002</v>
       </c>
       <c r="BY14" s="67">
@@ -39478,7 +40163,7 @@
         <v>97.410600000000002</v>
       </c>
       <c r="CF14" s="99">
-        <f t="shared" ref="CF14" si="287">CE14</f>
+        <f t="shared" ref="CF14" si="291">CE14</f>
         <v>97.410600000000002</v>
       </c>
       <c r="CI14" s="67">
@@ -39504,7 +40189,7 @@
         <v>111.32640000000001</v>
       </c>
       <c r="CP14" s="99">
-        <f t="shared" ref="CP14" si="288">CO14</f>
+        <f t="shared" ref="CP14" si="292">CO14</f>
         <v>111.32640000000001</v>
       </c>
       <c r="CQ14" s="67">
@@ -39530,7 +40215,7 @@
         <v>118.2843</v>
       </c>
       <c r="CX14" s="99">
-        <f t="shared" ref="CX14" si="289">CW14</f>
+        <f t="shared" ref="CX14" si="293">CW14</f>
         <v>118.2843</v>
       </c>
       <c r="CY14" s="67">
@@ -39556,7 +40241,7 @@
         <v>0</v>
       </c>
       <c r="DF14" s="142">
-        <f t="shared" ref="DF14" si="290">DE14</f>
+        <f t="shared" ref="DF14" si="294">DE14</f>
         <v>0</v>
       </c>
       <c r="DG14" s="67">
@@ -39582,7 +40267,7 @@
         <v>83.494799999999998</v>
       </c>
       <c r="DN14" s="140">
-        <f t="shared" ref="DN14" si="291">DM14</f>
+        <f t="shared" ref="DN14" si="295">DM14</f>
         <v>83.494799999999998</v>
       </c>
       <c r="DO14" s="67">
@@ -39608,7 +40293,7 @@
         <v>132.20010000000002</v>
       </c>
       <c r="DV14" s="140">
-        <f t="shared" ref="DV14" si="292">DU14</f>
+        <f t="shared" ref="DV14" si="296">DU14</f>
         <v>132.20010000000002</v>
       </c>
       <c r="DW14" s="67">
@@ -39795,7 +40480,7 @@
         <v>8.5489200000000007</v>
       </c>
       <c r="GE14" s="48">
-        <f t="shared" si="170"/>
+        <f t="shared" si="173"/>
         <v>136.78272000000001</v>
       </c>
       <c r="GF14" s="49"/>
@@ -39820,7 +40505,7 @@
         <v>7.3749000000000002</v>
       </c>
       <c r="GM14" s="48">
-        <f t="shared" si="171"/>
+        <f t="shared" si="174"/>
         <v>117.9984</v>
       </c>
       <c r="GN14" s="49"/>
@@ -39845,7 +40530,7 @@
         <v>7.3749000000000002</v>
       </c>
       <c r="GU14" s="48">
-        <f t="shared" si="172"/>
+        <f t="shared" si="175"/>
         <v>88.498800000000003</v>
       </c>
       <c r="GV14" s="49"/>
@@ -39870,7 +40555,7 @@
         <v>6.2670000000000003</v>
       </c>
       <c r="HC14" s="48">
-        <f t="shared" si="173"/>
+        <f t="shared" si="176"/>
         <v>94.00500000000001</v>
       </c>
       <c r="HD14" s="49"/>
@@ -39895,7 +40580,7 @@
         <v>6.2670000000000003</v>
       </c>
       <c r="HK14" s="48">
-        <f t="shared" si="174"/>
+        <f t="shared" si="177"/>
         <v>81.471000000000004</v>
       </c>
       <c r="HL14" s="49"/>
@@ -39920,7 +40605,7 @@
         <v>6.2670000000000003</v>
       </c>
       <c r="HS14" s="48">
-        <f t="shared" si="175"/>
+        <f t="shared" si="178"/>
         <v>106.539</v>
       </c>
       <c r="HT14" s="49"/>
@@ -39942,7 +40627,7 @@
         <v>6.2670000000000003</v>
       </c>
       <c r="IA14" s="48">
-        <f t="shared" si="176"/>
+        <f t="shared" si="179"/>
         <v>94.00500000000001</v>
       </c>
       <c r="IB14" s="49"/>
@@ -39964,7 +40649,7 @@
         <v>6.9139920000000004</v>
       </c>
       <c r="II14" s="48">
-        <f t="shared" si="177"/>
+        <f t="shared" si="180"/>
         <v>117.53786400000001</v>
       </c>
       <c r="IJ14" s="49"/>
@@ -39988,7 +40673,7 @@
         <v>5.8684919999999998</v>
       </c>
       <c r="IQ14" s="48">
-        <f t="shared" si="178"/>
+        <f t="shared" si="181"/>
         <v>88.027379999999994</v>
       </c>
       <c r="IR14" s="49"/>
@@ -40005,14 +40690,14 @@
         <v>507</v>
       </c>
       <c r="IW14" s="46">
-        <f t="shared" si="276"/>
+        <f t="shared" si="280"/>
         <v>15</v>
       </c>
       <c r="IX14" s="48">
         <v>5.8684919999999998</v>
       </c>
       <c r="IY14" s="48">
-        <f t="shared" si="179"/>
+        <f t="shared" si="182"/>
         <v>88.027379999999994</v>
       </c>
       <c r="IZ14" s="49"/>
@@ -40029,14 +40714,14 @@
         <v>522</v>
       </c>
       <c r="JE14" s="46">
-        <f t="shared" si="277"/>
+        <f t="shared" si="281"/>
         <v>17</v>
       </c>
       <c r="JF14" s="48">
         <v>4.3260719999999999</v>
       </c>
       <c r="JG14" s="48">
-        <f t="shared" si="180"/>
+        <f t="shared" si="183"/>
         <v>73.543223999999995</v>
       </c>
       <c r="JH14" s="49"/>
@@ -40051,14 +40736,14 @@
         <v>539</v>
       </c>
       <c r="JM14" s="46">
-        <f t="shared" si="278"/>
+        <f t="shared" si="282"/>
         <v>18</v>
       </c>
       <c r="JN14" s="48">
         <v>4.3260719999999999</v>
       </c>
       <c r="JO14" s="48">
-        <f t="shared" si="181"/>
+        <f t="shared" si="184"/>
         <v>77.869295999999991</v>
       </c>
       <c r="JP14" s="49"/>
@@ -40076,14 +40761,14 @@
         <v>557</v>
       </c>
       <c r="JU14" s="46">
-        <f t="shared" si="279"/>
+        <f t="shared" si="283"/>
         <v>6</v>
       </c>
       <c r="JV14" s="48">
         <v>4.3260719999999999</v>
       </c>
       <c r="JW14" s="48">
-        <f t="shared" si="182"/>
+        <f t="shared" si="185"/>
         <v>25.956432</v>
       </c>
       <c r="JX14" s="49"/>
@@ -40101,14 +40786,14 @@
         <v>563</v>
       </c>
       <c r="KC14" s="46">
-        <f t="shared" si="280"/>
+        <f t="shared" si="284"/>
         <v>8</v>
       </c>
       <c r="KD14" s="48">
         <v>4.3260719999999999</v>
       </c>
       <c r="KE14" s="48">
-        <f t="shared" si="183"/>
+        <f t="shared" si="186"/>
         <v>34.608575999999999</v>
       </c>
       <c r="KF14" s="49"/>
@@ -40126,14 +40811,14 @@
         <v>571</v>
       </c>
       <c r="KK14" s="46">
-        <f t="shared" si="281"/>
+        <f t="shared" si="285"/>
         <v>6</v>
       </c>
       <c r="KL14" s="48">
         <v>4.3260719999999999</v>
       </c>
       <c r="KM14" s="48">
-        <f t="shared" si="184"/>
+        <f t="shared" si="187"/>
         <v>25.956432</v>
       </c>
       <c r="KN14" s="49"/>
@@ -40151,14 +40836,14 @@
         <v>577</v>
       </c>
       <c r="KS14" s="46">
-        <f t="shared" si="282"/>
+        <f t="shared" si="286"/>
         <v>9</v>
       </c>
       <c r="KT14" s="48">
         <v>5.5</v>
       </c>
       <c r="KU14" s="48">
-        <f t="shared" si="185"/>
+        <f t="shared" si="188"/>
         <v>49.5</v>
       </c>
       <c r="KV14" s="49"/>
@@ -40176,14 +40861,14 @@
         <v>586</v>
       </c>
       <c r="LA14" s="46">
-        <f t="shared" si="283"/>
+        <f t="shared" si="287"/>
         <v>11</v>
       </c>
       <c r="LB14" s="48">
         <v>5.5</v>
       </c>
       <c r="LC14" s="48">
-        <f t="shared" si="186"/>
+        <f t="shared" si="189"/>
         <v>60.5</v>
       </c>
       <c r="LD14" s="49"/>
@@ -40201,14 +40886,14 @@
         <v>597</v>
       </c>
       <c r="LI14" s="46">
-        <f t="shared" si="284"/>
+        <f t="shared" si="288"/>
         <v>14</v>
       </c>
       <c r="LJ14" s="48">
         <v>6.7729999999999997</v>
       </c>
       <c r="LK14" s="48">
-        <f t="shared" si="187"/>
+        <f t="shared" si="190"/>
         <v>94.822000000000003</v>
       </c>
       <c r="LL14" s="49"/>
@@ -40226,14 +40911,14 @@
         <v>611</v>
       </c>
       <c r="LQ14" s="46">
-        <f t="shared" si="285"/>
+        <f t="shared" si="289"/>
         <v>17</v>
       </c>
       <c r="LR14" s="48">
         <v>6.7729999999999997</v>
       </c>
       <c r="LS14" s="48">
-        <f t="shared" si="286"/>
+        <f t="shared" si="290"/>
         <v>115.14099999999999</v>
       </c>
       <c r="LT14" s="49"/>
@@ -40251,7 +40936,7 @@
         <v>628</v>
       </c>
       <c r="LY14" s="46">
-        <f t="shared" ref="LY14" si="293">LW14-LX14</f>
+        <f t="shared" ref="LY14" si="297">LW14-LX14</f>
         <v>12</v>
       </c>
       <c r="LZ14" s="48">
@@ -40276,7 +40961,7 @@
         <v>640</v>
       </c>
       <c r="MH14" s="46">
-        <f t="shared" ref="MH14" si="294">MF14-MG14</f>
+        <f t="shared" ref="MH14" si="298">MF14-MG14</f>
         <v>12</v>
       </c>
       <c r="MI14" s="48">
@@ -41354,11 +42039,42 @@
         <f>ZB14</f>
         <v>95.52</v>
       </c>
-      <c r="ZD14" s="324">
+      <c r="ZD14" s="339">
         <v>87.53</v>
       </c>
-    </row>
-    <row r="15" spans="2:680" x14ac:dyDescent="0.25">
+      <c r="ZE14" s="87" t="s">
+        <v>237</v>
+      </c>
+      <c r="ZF14" s="280">
+        <v>1090</v>
+      </c>
+      <c r="ZG14" s="280">
+        <v>1071</v>
+      </c>
+      <c r="ZH14" s="46">
+        <f>ZF14-ZG14</f>
+        <v>19</v>
+      </c>
+      <c r="ZI14" s="48">
+        <v>7.96</v>
+      </c>
+      <c r="ZJ14" s="48">
+        <f>ZH14*ZI14</f>
+        <v>151.24</v>
+      </c>
+      <c r="ZK14" s="49">
+        <f>ZJ14</f>
+        <v>151.24</v>
+      </c>
+      <c r="ZL14" s="306">
+        <f>ZK14</f>
+        <v>151.24</v>
+      </c>
+      <c r="ZM14" s="324">
+        <v>87.53</v>
+      </c>
+    </row>
+    <row r="15" spans="2:689" x14ac:dyDescent="0.25">
       <c r="B15" s="229">
         <v>330152984</v>
       </c>
@@ -42239,8 +42955,20 @@
       <c r="ZD15" s="323">
         <v>6.67</v>
       </c>
-    </row>
-    <row r="16" spans="2:680" x14ac:dyDescent="0.25">
+      <c r="ZF15" s="152"/>
+      <c r="ZG15" s="313"/>
+      <c r="ZH15" s="46"/>
+      <c r="ZI15" s="48"/>
+      <c r="ZJ15" s="48"/>
+      <c r="ZK15" s="49"/>
+      <c r="ZL15" s="306">
+        <v>6.67</v>
+      </c>
+      <c r="ZM15" s="323">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="16" spans="2:689" x14ac:dyDescent="0.25">
       <c r="B16" s="46">
         <v>301033</v>
       </c>
@@ -43024,8 +43752,16 @@
       <c r="ZB16" s="49"/>
       <c r="ZC16" s="306"/>
       <c r="ZD16" s="75"/>
-    </row>
-    <row r="17" spans="2:680" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="ZF16" s="152"/>
+      <c r="ZG16" s="313"/>
+      <c r="ZH16" s="46"/>
+      <c r="ZI16" s="48"/>
+      <c r="ZJ16" s="48"/>
+      <c r="ZK16" s="49"/>
+      <c r="ZL16" s="306"/>
+      <c r="ZM16" s="75"/>
+    </row>
+    <row r="17" spans="2:689" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="46"/>
       <c r="C17" s="47" t="s">
         <v>56</v>
@@ -43088,7 +43824,7 @@
       <c r="AX17" s="72"/>
       <c r="AY17" s="102"/>
       <c r="AZ17" s="99">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="BA17" s="69"/>
@@ -43099,7 +43835,7 @@
       <c r="BF17" s="72"/>
       <c r="BG17" s="102"/>
       <c r="BH17" s="99">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="BI17" s="69"/>
@@ -43110,7 +43846,7 @@
       <c r="BN17" s="72"/>
       <c r="BO17" s="102"/>
       <c r="BP17" s="99">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0</v>
       </c>
       <c r="BQ17" s="69"/>
@@ -43121,7 +43857,7 @@
       <c r="BV17" s="72"/>
       <c r="BW17" s="102"/>
       <c r="BX17" s="99">
-        <f t="shared" si="228"/>
+        <f t="shared" si="232"/>
         <v>0</v>
       </c>
       <c r="BY17" s="69"/>
@@ -43788,8 +44524,16 @@
       <c r="ZB17" s="72"/>
       <c r="ZC17" s="317"/>
       <c r="ZD17" s="318"/>
-    </row>
-    <row r="18" spans="2:680" x14ac:dyDescent="0.25">
+      <c r="ZF17" s="69"/>
+      <c r="ZG17" s="70"/>
+      <c r="ZH17" s="70"/>
+      <c r="ZI17" s="71"/>
+      <c r="ZJ17" s="71"/>
+      <c r="ZK17" s="72"/>
+      <c r="ZL17" s="317"/>
+      <c r="ZM17" s="318"/>
+    </row>
+    <row r="18" spans="2:689" x14ac:dyDescent="0.25">
       <c r="B18" s="74"/>
       <c r="C18" s="47" t="s">
         <v>208</v>
@@ -44087,7 +44831,7 @@
         <v>4718.3940000000002</v>
       </c>
     </row>
-    <row r="19" spans="2:680" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:689" x14ac:dyDescent="0.25">
       <c r="FH19" s="191" t="s">
         <v>175</v>
       </c>
@@ -44116,7 +44860,7 @@
         <v>1494.84</v>
       </c>
     </row>
-    <row r="20" spans="2:680" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:689" x14ac:dyDescent="0.25">
       <c r="FJ20" s="184">
         <f>FJ18+FJ19</f>
         <v>4782.152</v>
@@ -44128,7 +44872,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="2:680" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:689" x14ac:dyDescent="0.25">
       <c r="FI21" s="187" t="s">
         <v>176</v>
       </c>
@@ -44146,7 +44890,7 @@
         <v>125.47199999999999</v>
       </c>
     </row>
-    <row r="22" spans="2:680" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:689" x14ac:dyDescent="0.25">
       <c r="FI22" s="190" t="s">
         <v>177</v>
       </c>
@@ -44164,7 +44908,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="2:680" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:689" x14ac:dyDescent="0.25">
       <c r="FI23" s="185" t="s">
         <v>178</v>
       </c>
@@ -44190,7 +44934,73 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="81">
+  <mergeCells count="82">
+    <mergeCell ref="ZF1:ZM1"/>
+    <mergeCell ref="YN1:YU1"/>
+    <mergeCell ref="XV1:YC1"/>
+    <mergeCell ref="XD1:XK1"/>
+    <mergeCell ref="WU1:XB1"/>
+    <mergeCell ref="VT1:WA1"/>
+    <mergeCell ref="WC1:WJ1"/>
+    <mergeCell ref="XM1:XT1"/>
+    <mergeCell ref="YE1:YL1"/>
+    <mergeCell ref="VB1:VI1"/>
+    <mergeCell ref="WL1:WS1"/>
+    <mergeCell ref="OJ1:OQ1"/>
+    <mergeCell ref="QP1:QW1"/>
+    <mergeCell ref="TR1:TY1"/>
+    <mergeCell ref="PH1:PO1"/>
+    <mergeCell ref="QG1:QN1"/>
+    <mergeCell ref="PY1:QF1"/>
+    <mergeCell ref="QX1:RE1"/>
+    <mergeCell ref="BA1:BH1"/>
+    <mergeCell ref="BY1:CF1"/>
+    <mergeCell ref="BQ1:BX1"/>
+    <mergeCell ref="BI1:BP1"/>
+    <mergeCell ref="ND1:NK1"/>
+    <mergeCell ref="KA1:KH1"/>
+    <mergeCell ref="MV1:NC1"/>
+    <mergeCell ref="MF1:MM1"/>
+    <mergeCell ref="LW1:MD1"/>
+    <mergeCell ref="LO1:LV1"/>
+    <mergeCell ref="KY1:LF1"/>
+    <mergeCell ref="MN1:MU1"/>
+    <mergeCell ref="CI1:CP1"/>
+    <mergeCell ref="DW1:ED1"/>
+    <mergeCell ref="DO1:DV1"/>
+    <mergeCell ref="DG1:DN1"/>
+    <mergeCell ref="EU1:FB1"/>
+    <mergeCell ref="CY1:DF1"/>
+    <mergeCell ref="EM1:ET1"/>
+    <mergeCell ref="CQ1:CX1"/>
+    <mergeCell ref="EE1:EL1"/>
+    <mergeCell ref="AS1:AZ1"/>
+    <mergeCell ref="E1:L1"/>
+    <mergeCell ref="M1:T1"/>
+    <mergeCell ref="U1:AB1"/>
+    <mergeCell ref="AC1:AJ1"/>
+    <mergeCell ref="AK1:AR1"/>
+    <mergeCell ref="GQ1:GX1"/>
+    <mergeCell ref="GA1:GH1"/>
+    <mergeCell ref="LG1:LN1"/>
+    <mergeCell ref="FC1:FJ1"/>
+    <mergeCell ref="FK1:FR1"/>
+    <mergeCell ref="HO1:HV1"/>
+    <mergeCell ref="IE1:IL1"/>
+    <mergeCell ref="IU1:JB1"/>
+    <mergeCell ref="KQ1:KX1"/>
+    <mergeCell ref="FS1:FZ1"/>
+    <mergeCell ref="GI1:GP1"/>
+    <mergeCell ref="HG1:HN1"/>
+    <mergeCell ref="GY1:HF1"/>
+    <mergeCell ref="NT1:OA1"/>
+    <mergeCell ref="IM1:IT1"/>
+    <mergeCell ref="HW1:ID1"/>
+    <mergeCell ref="NL1:NS1"/>
+    <mergeCell ref="JK1:JR1"/>
+    <mergeCell ref="KI1:KP1"/>
+    <mergeCell ref="JS1:JZ1"/>
+    <mergeCell ref="JC1:JJ1"/>
     <mergeCell ref="YW1:ZD1"/>
     <mergeCell ref="OB1:OI1"/>
     <mergeCell ref="TI1:TP1"/>
@@ -44207,71 +45017,6 @@
     <mergeCell ref="RP1:RW1"/>
     <mergeCell ref="PP1:PW1"/>
     <mergeCell ref="SQ1:SX1"/>
-    <mergeCell ref="NT1:OA1"/>
-    <mergeCell ref="IM1:IT1"/>
-    <mergeCell ref="HW1:ID1"/>
-    <mergeCell ref="NL1:NS1"/>
-    <mergeCell ref="JK1:JR1"/>
-    <mergeCell ref="KI1:KP1"/>
-    <mergeCell ref="JS1:JZ1"/>
-    <mergeCell ref="JC1:JJ1"/>
-    <mergeCell ref="GQ1:GX1"/>
-    <mergeCell ref="GA1:GH1"/>
-    <mergeCell ref="LG1:LN1"/>
-    <mergeCell ref="FC1:FJ1"/>
-    <mergeCell ref="FK1:FR1"/>
-    <mergeCell ref="HO1:HV1"/>
-    <mergeCell ref="IE1:IL1"/>
-    <mergeCell ref="IU1:JB1"/>
-    <mergeCell ref="KQ1:KX1"/>
-    <mergeCell ref="FS1:FZ1"/>
-    <mergeCell ref="GI1:GP1"/>
-    <mergeCell ref="HG1:HN1"/>
-    <mergeCell ref="GY1:HF1"/>
-    <mergeCell ref="AS1:AZ1"/>
-    <mergeCell ref="E1:L1"/>
-    <mergeCell ref="M1:T1"/>
-    <mergeCell ref="U1:AB1"/>
-    <mergeCell ref="AC1:AJ1"/>
-    <mergeCell ref="AK1:AR1"/>
-    <mergeCell ref="EU1:FB1"/>
-    <mergeCell ref="CY1:DF1"/>
-    <mergeCell ref="EM1:ET1"/>
-    <mergeCell ref="CQ1:CX1"/>
-    <mergeCell ref="EE1:EL1"/>
-    <mergeCell ref="BA1:BH1"/>
-    <mergeCell ref="BY1:CF1"/>
-    <mergeCell ref="BQ1:BX1"/>
-    <mergeCell ref="BI1:BP1"/>
-    <mergeCell ref="ND1:NK1"/>
-    <mergeCell ref="KA1:KH1"/>
-    <mergeCell ref="MV1:NC1"/>
-    <mergeCell ref="MF1:MM1"/>
-    <mergeCell ref="LW1:MD1"/>
-    <mergeCell ref="LO1:LV1"/>
-    <mergeCell ref="KY1:LF1"/>
-    <mergeCell ref="MN1:MU1"/>
-    <mergeCell ref="CI1:CP1"/>
-    <mergeCell ref="DW1:ED1"/>
-    <mergeCell ref="DO1:DV1"/>
-    <mergeCell ref="DG1:DN1"/>
-    <mergeCell ref="VB1:VI1"/>
-    <mergeCell ref="WL1:WS1"/>
-    <mergeCell ref="OJ1:OQ1"/>
-    <mergeCell ref="QP1:QW1"/>
-    <mergeCell ref="TR1:TY1"/>
-    <mergeCell ref="PH1:PO1"/>
-    <mergeCell ref="QG1:QN1"/>
-    <mergeCell ref="PY1:QF1"/>
-    <mergeCell ref="QX1:RE1"/>
-    <mergeCell ref="YN1:YU1"/>
-    <mergeCell ref="XV1:YC1"/>
-    <mergeCell ref="XD1:XK1"/>
-    <mergeCell ref="WU1:XB1"/>
-    <mergeCell ref="VT1:WA1"/>
-    <mergeCell ref="WC1:WJ1"/>
-    <mergeCell ref="XM1:XT1"/>
-    <mergeCell ref="YE1:YL1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="31" orientation="landscape" r:id="rId1"/>
@@ -44285,7 +45030,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB37273-15E9-47B1-9B41-2A454D073757}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -45044,8 +45798,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:T31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -45626,8 +46380,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A2:M19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -46058,8 +46812,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A2:M20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -46491,405 +47245,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:M19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2">
-        <v>43077</v>
-      </c>
-      <c r="D2" s="2">
-        <v>43091</v>
-      </c>
-      <c r="E2" s="3">
-        <f>D2-C2</f>
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="325" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="326"/>
-      <c r="D3" s="326"/>
-      <c r="E3" s="334"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5">
-        <v>6900</v>
-      </c>
-      <c r="D4" s="6">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6">
-        <f>C4*D4</f>
-        <v>6900</v>
-      </c>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="105"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6">
-        <f>C5*D5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="327" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="328"/>
-      <c r="D6" s="328"/>
-      <c r="E6" s="335"/>
-    </row>
-    <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="124" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="125" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="126">
-        <v>0</v>
-      </c>
-      <c r="D7" s="127">
-        <v>0</v>
-      </c>
-      <c r="E7" s="147">
-        <f>C7*D7</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="151"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="150"/>
-      <c r="K7" s="150"/>
-      <c r="L7" s="150"/>
-      <c r="M7" s="150"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="103" t="s">
-        <v>160</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" s="9">
-        <v>500</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="148">
-        <f t="shared" ref="E8:E16" si="0">C8*D8</f>
-        <v>500</v>
-      </c>
-      <c r="F8" s="150"/>
-      <c r="G8" s="150"/>
-      <c r="H8" s="150"/>
-      <c r="I8" s="150"/>
-      <c r="J8" s="150"/>
-      <c r="K8" s="150"/>
-      <c r="L8" s="150"/>
-      <c r="M8" s="150"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="103"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="148"/>
-      <c r="F9" s="150"/>
-      <c r="G9" s="150"/>
-      <c r="H9" s="150"/>
-      <c r="I9" s="150"/>
-      <c r="J9" s="150"/>
-      <c r="K9" s="150"/>
-      <c r="L9" s="150"/>
-      <c r="M9" s="150"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="103" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="9">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0</v>
-      </c>
-      <c r="E10" s="148">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="150"/>
-      <c r="G10" s="150"/>
-      <c r="H10" s="151"/>
-      <c r="I10" s="150"/>
-      <c r="J10" s="150"/>
-      <c r="K10" s="150"/>
-      <c r="L10" s="150"/>
-      <c r="M10" s="150"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="103"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="148">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="150"/>
-      <c r="G11" s="150"/>
-      <c r="H11" s="150"/>
-      <c r="I11" s="150"/>
-      <c r="J11" s="150"/>
-      <c r="K11" s="150"/>
-      <c r="L11" s="150"/>
-      <c r="M11" s="150"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="103" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="9">
-        <v>0</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0</v>
-      </c>
-      <c r="E12" s="148">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F12" s="150"/>
-      <c r="G12" s="150"/>
-      <c r="H12" s="150"/>
-      <c r="I12" s="151"/>
-      <c r="J12" s="150"/>
-      <c r="K12" s="150"/>
-      <c r="L12" s="150"/>
-      <c r="M12" s="150"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="103"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="9">
-        <v>0</v>
-      </c>
-      <c r="D13" s="8">
-        <v>0</v>
-      </c>
-      <c r="E13" s="148">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="150"/>
-      <c r="G13" s="150"/>
-      <c r="H13" s="150"/>
-      <c r="I13" s="151"/>
-      <c r="J13" s="150"/>
-      <c r="K13" s="150"/>
-      <c r="L13" s="150"/>
-      <c r="M13" s="150"/>
-    </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="103" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="9">
-        <v>2400</v>
-      </c>
-      <c r="D14" s="8">
-        <v>1</v>
-      </c>
-      <c r="E14" s="148">
-        <f t="shared" si="0"/>
-        <v>2400</v>
-      </c>
-      <c r="F14" s="150"/>
-      <c r="G14" s="150"/>
-      <c r="H14" s="150"/>
-      <c r="I14" s="150"/>
-      <c r="J14" s="150"/>
-      <c r="K14" s="151"/>
-      <c r="L14" s="150"/>
-      <c r="M14" s="150"/>
-    </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="103"/>
-      <c r="B15" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="C15" s="9">
-        <v>1000</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1</v>
-      </c>
-      <c r="E15" s="148">
-        <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="F15" s="150"/>
-      <c r="G15" s="150"/>
-      <c r="H15" s="150"/>
-      <c r="I15" s="150"/>
-      <c r="J15" s="150"/>
-      <c r="K15" s="149"/>
-      <c r="L15" s="150"/>
-      <c r="M15" s="150"/>
-    </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="103"/>
-      <c r="B16" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="C16" s="9">
-        <v>500</v>
-      </c>
-      <c r="D16" s="8">
-        <v>1</v>
-      </c>
-      <c r="E16" s="148">
-        <f t="shared" si="0"/>
-        <v>500</v>
-      </c>
-      <c r="F16" s="150"/>
-      <c r="G16" s="150"/>
-      <c r="H16" s="150"/>
-      <c r="I16" s="150"/>
-      <c r="J16" s="150"/>
-      <c r="K16" s="149"/>
-      <c r="L16" s="150"/>
-      <c r="M16" s="150"/>
-    </row>
-    <row r="17" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E17" s="92">
-        <f>SUM(E4:E5)</f>
-        <v>6900</v>
-      </c>
-      <c r="F17" s="88">
-        <f t="shared" ref="F17:K17" si="1">SUM(F3:F16)</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="88">
-        <f>SUM(L7:L16)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="93">
-        <f>SUM(F17:L17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E18" s="41">
-        <f>SUM(E7:E16)</f>
-        <v>4400</v>
-      </c>
-      <c r="J18" s="88"/>
-    </row>
-    <row r="19" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E19" s="43">
-        <f>E17-E18</f>
-        <v>2500</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B6:E6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>